--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -12,7 +12,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CO$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -21,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -37,6 +38,11 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,11 +73,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -135,61 +136,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,6 +198,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -272,6 +297,108 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO8" headerRowCount="1">
+  <autoFilter ref="A1:CO8"/>
+  <tableColumns count="93">
+    <tableColumn id="1" name="pick_id"/>
+    <tableColumn id="2" name="created_at_utc"/>
+    <tableColumn id="3" name="event_start_utc"/>
+    <tableColumn id="4" name="event_id"/>
+    <tableColumn id="5" name="league"/>
+    <tableColumn id="6" name="away_team"/>
+    <tableColumn id="7" name="home_team"/>
+    <tableColumn id="8" name="market_type"/>
+    <tableColumn id="9" name="selection"/>
+    <tableColumn id="10" name="line"/>
+    <tableColumn id="11" name="sportsbook"/>
+    <tableColumn id="12" name="american_odds"/>
+    <tableColumn id="13" name="decimal_odds"/>
+    <tableColumn id="14" name="market_implied_probability"/>
+    <tableColumn id="15" name="model_probability"/>
+    <tableColumn id="16" name="model_uncertainty"/>
+    <tableColumn id="17" name="edge"/>
+    <tableColumn id="18" name="confidence_score"/>
+    <tableColumn id="19" name="units"/>
+    <tableColumn id="20" name="model_version"/>
+    <tableColumn id="21" name="status"/>
+    <tableColumn id="22" name="result"/>
+    <tableColumn id="23" name="away_score"/>
+    <tableColumn id="24" name="home_score"/>
+    <tableColumn id="25" name="closing_line"/>
+    <tableColumn id="26" name="closing_american_odds"/>
+    <tableColumn id="27" name="closing_implied_probability"/>
+    <tableColumn id="28" name="probability_clv"/>
+    <tableColumn id="29" name="pnl_units"/>
+    <tableColumn id="30" name="settled_at_utc"/>
+    <tableColumn id="31" name="rationale"/>
+    <tableColumn id="32" name="risks"/>
+    <tableColumn id="33" name="review_status"/>
+    <tableColumn id="34" name="loss_classification"/>
+    <tableColumn id="35" name="loss_cause"/>
+    <tableColumn id="36" name="corrective_action"/>
+    <tableColumn id="37" name="call_type"/>
+    <tableColumn id="38" name="ledger_schema_version"/>
+    <tableColumn id="39" name="record_type"/>
+    <tableColumn id="40" name="decision"/>
+    <tableColumn id="41" name="reason_code"/>
+    <tableColumn id="42" name="canonical_away_team_id"/>
+    <tableColumn id="43" name="canonical_away_team_name"/>
+    <tableColumn id="44" name="original_away_team"/>
+    <tableColumn id="45" name="canonical_home_team_id"/>
+    <tableColumn id="46" name="canonical_home_team_name"/>
+    <tableColumn id="47" name="original_home_team"/>
+    <tableColumn id="48" name="banned_team_id"/>
+    <tableColumn id="49" name="banned_team_name"/>
+    <tableColumn id="50" name="model_origin"/>
+    <tableColumn id="51" name="baseline_identifier"/>
+    <tableColumn id="52" name="model_state_at_decision"/>
+    <tableColumn id="53" name="model_artifact_hash"/>
+    <tableColumn id="54" name="calibration_method"/>
+    <tableColumn id="55" name="calibration_version"/>
+    <tableColumn id="56" name="calibration_artifact_hash"/>
+    <tableColumn id="57" name="feature_schema_version"/>
+    <tableColumn id="58" name="entity_map_version"/>
+    <tableColumn id="59" name="code_revision"/>
+    <tableColumn id="60" name="observed_at_utc"/>
+    <tableColumn id="61" name="correlation_tags"/>
+    <tableColumn id="62" name="decision_line"/>
+    <tableColumn id="63" name="decision_american_odds"/>
+    <tableColumn id="64" name="decision_decimal_odds"/>
+    <tableColumn id="65" name="decision_raw_implied_probability"/>
+    <tableColumn id="66" name="decision_no_vig_probability"/>
+    <tableColumn id="67" name="decision_consensus_probability"/>
+    <tableColumn id="68" name="decision_consensus_line"/>
+    <tableColumn id="69" name="closing_decimal_odds"/>
+    <tableColumn id="70" name="closing_raw_implied_probability"/>
+    <tableColumn id="71" name="closing_no_vig_probability"/>
+    <tableColumn id="72" name="closing_consensus_probability"/>
+    <tableColumn id="73" name="closing_consensus_line"/>
+    <tableColumn id="74" name="legacy_units"/>
+    <tableColumn id="75" name="void_reason"/>
+    <tableColumn id="76" name="research_score_units"/>
+    <tableColumn id="77" name="research_pnl_units"/>
+    <tableColumn id="78" name="research_scored_at_utc"/>
+    <tableColumn id="79" name="research_scoring_note"/>
+    <tableColumn id="80" name="migrated_from_version"/>
+    <tableColumn id="81" name="elo_probability"/>
+    <tableColumn id="82" name="trend_gap"/>
+    <tableColumn id="83" name="park_factor"/>
+    <tableColumn id="84" name="weather_factor"/>
+    <tableColumn id="85" name="pitcher_era_gap"/>
+    <tableColumn id="86" name="probable_starter_era_gap"/>
+    <tableColumn id="87" name="unavailable_features"/>
+    <tableColumn id="88" name="defensive_trend_gap"/>
+    <tableColumn id="89" name="neutral_elo_rating_difference"/>
+    <tableColumn id="90" name="rest_disparity"/>
+    <tableColumn id="91" name="back_to_back_gap"/>
+    <tableColumn id="92" name="games_last_7_gap"/>
+    <tableColumn id="93" name="schedule_missingness"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -625,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$2)</f>
+        <f>COUNTA('Picks'!$A$2:$A$8)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$8,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -665,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$2,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$8,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")/(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")/(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$2)/SUM('Picks'!$BX$2:$BX$2),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$8)/SUM('Picks'!$BX$2:$BX$8),0)</f>
         <v/>
       </c>
     </row>
@@ -705,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$2)</f>
+        <f>SUM('Picks'!$BY$2:$BY$8)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$2,"&lt;&gt;",'Picks'!$AB$2:$AB$2),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$8,"&lt;&gt;",'Picks'!$AB$2:$AB$8),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$2,'Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$8,'Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -772,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -788,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -803,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -819,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -834,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -850,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -883,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO1"/>
+  <dimension ref="A1:CO8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1448,9 +1575,1908 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>b23f046d636545d4</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:51:39.691788Z</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>61045</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>SaD GC</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>ORA Temper</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="n"/>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="M2" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N2" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="O2" s="28" t="n">
+        <v>0.5057199999999999</v>
+      </c>
+      <c r="P2" s="28" t="n"/>
+      <c r="Q2" s="28" t="n">
+        <v>0.175687</v>
+      </c>
+      <c r="R2" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S2" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T2" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U2" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="25" t="n"/>
+      <c r="Z2" s="26" t="n"/>
+      <c r="AA2" s="28" t="n"/>
+      <c r="AB2" s="28" t="n"/>
+      <c r="AC2" s="30" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="AD2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:52:08.770740Z</t>
+        </is>
+      </c>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-valorant-orat-sga-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG2" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH2" s="24" t="n"/>
+      <c r="AI2" s="31" t="n"/>
+      <c r="AJ2" s="31" t="n"/>
+      <c r="AK2" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN2" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP2" s="24" t="inlineStr">
+        <is>
+          <t>SaD GC</t>
+        </is>
+      </c>
+      <c r="AQ2" s="24" t="inlineStr">
+        <is>
+          <t>SaD GC</t>
+        </is>
+      </c>
+      <c r="AR2" s="24" t="inlineStr">
+        <is>
+          <t>SaD GC</t>
+        </is>
+      </c>
+      <c r="AS2" s="24" t="inlineStr">
+        <is>
+          <t>ORA Temper</t>
+        </is>
+      </c>
+      <c r="AT2" s="24" t="inlineStr">
+        <is>
+          <t>ORA Temper</t>
+        </is>
+      </c>
+      <c r="AU2" s="24" t="inlineStr">
+        <is>
+          <t>ORA Temper</t>
+        </is>
+      </c>
+      <c r="AV2" s="24" t="n"/>
+      <c r="AW2" s="24" t="n"/>
+      <c r="AX2" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY2" s="24" t="n"/>
+      <c r="AZ2" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA2" s="24" t="inlineStr">
+        <is>
+          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+        </is>
+      </c>
+      <c r="BB2" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC2" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD2" s="24" t="inlineStr">
+        <is>
+          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+        </is>
+      </c>
+      <c r="BE2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG2" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH2" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:51:33.586186Z</t>
+        </is>
+      </c>
+      <c r="BI2" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ2" s="25" t="n"/>
+      <c r="BK2" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="BL2" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BM2" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="BN2" s="28" t="n"/>
+      <c r="BO2" s="28" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
+      <c r="BR2" s="28" t="n"/>
+      <c r="BS2" s="28" t="n"/>
+      <c r="BT2" s="28" t="n"/>
+      <c r="BU2" s="25" t="n"/>
+      <c r="BV2" s="29" t="n"/>
+      <c r="BW2" s="24" t="n"/>
+      <c r="BX2" s="30" t="n"/>
+      <c r="BY2" s="27" t="n"/>
+      <c r="BZ2" s="24" t="n"/>
+      <c r="CA2" s="31" t="n"/>
+      <c r="CB2" s="24" t="n"/>
+      <c r="CC2" s="24" t="n"/>
+      <c r="CD2" s="24" t="n"/>
+      <c r="CE2" s="24" t="n"/>
+      <c r="CF2" s="24" t="n"/>
+      <c r="CG2" s="24" t="n"/>
+      <c r="CH2" s="24" t="n"/>
+      <c r="CI2" s="24" t="n"/>
+      <c r="CJ2" s="24" t="n"/>
+      <c r="CK2" s="24" t="n"/>
+      <c r="CL2" s="24" t="n"/>
+      <c r="CM2" s="24" t="n"/>
+      <c r="CN2" s="24" t="n"/>
+      <c r="CO2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>2f0f151c797c42df</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:51:39.691788Z</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>61046</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 GC</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L3" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O3" s="28" t="n">
+        <v>0.53613</v>
+      </c>
+      <c r="P3" s="28" t="n"/>
+      <c r="Q3" s="28" t="n">
+        <v>0.03613</v>
+      </c>
+      <c r="R3" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="S3" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T3" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U3" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="26" t="n"/>
+      <c r="AA3" s="28" t="n"/>
+      <c r="AB3" s="28" t="n"/>
+      <c r="AC3" s="30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:57:20.308333Z</t>
+        </is>
+      </c>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-valorant-c9gc-spi-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG3" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH3" s="24" t="n"/>
+      <c r="AI3" s="31" t="n"/>
+      <c r="AJ3" s="31" t="n"/>
+      <c r="AK3" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN3" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP3" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AQ3" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AS3" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 GC</t>
+        </is>
+      </c>
+      <c r="AT3" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 GC</t>
+        </is>
+      </c>
+      <c r="AU3" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 GC</t>
+        </is>
+      </c>
+      <c r="AV3" s="24" t="n"/>
+      <c r="AW3" s="24" t="n"/>
+      <c r="AX3" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY3" s="24" t="n"/>
+      <c r="AZ3" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA3" s="24" t="inlineStr">
+        <is>
+          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+        </is>
+      </c>
+      <c r="BB3" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC3" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD3" s="24" t="inlineStr">
+        <is>
+          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+        </is>
+      </c>
+      <c r="BE3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG3" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH3" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:51:34.129373Z</t>
+        </is>
+      </c>
+      <c r="BI3" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ3" s="25" t="n"/>
+      <c r="BK3" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL3" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM3" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN3" s="28" t="n"/>
+      <c r="BO3" s="28" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
+      <c r="BR3" s="28" t="n"/>
+      <c r="BS3" s="28" t="n"/>
+      <c r="BT3" s="28" t="n"/>
+      <c r="BU3" s="25" t="n"/>
+      <c r="BV3" s="29" t="n"/>
+      <c r="BW3" s="24" t="n"/>
+      <c r="BX3" s="30" t="n"/>
+      <c r="BY3" s="27" t="n"/>
+      <c r="BZ3" s="24" t="n"/>
+      <c r="CA3" s="31" t="n"/>
+      <c r="CB3" s="24" t="n"/>
+      <c r="CC3" s="24" t="n"/>
+      <c r="CD3" s="24" t="n"/>
+      <c r="CE3" s="24" t="n"/>
+      <c r="CF3" s="24" t="n"/>
+      <c r="CG3" s="24" t="n"/>
+      <c r="CH3" s="24" t="n"/>
+      <c r="CI3" s="24" t="n"/>
+      <c r="CJ3" s="24" t="n"/>
+      <c r="CK3" s="24" t="n"/>
+      <c r="CL3" s="24" t="n"/>
+      <c r="CM3" s="24" t="n"/>
+      <c r="CN3" s="24" t="n"/>
+      <c r="CO3" s="24" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>b1750c0ef619421b</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:51:39.691788Z</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>61048</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Gold</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I4" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L4" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M4" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O4" s="28" t="n">
+        <v>0.541059</v>
+      </c>
+      <c r="P4" s="28" t="n"/>
+      <c r="Q4" s="28" t="n">
+        <v>0.041059</v>
+      </c>
+      <c r="R4" s="26" t="n">
+        <v>41</v>
+      </c>
+      <c r="S4" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U4" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="26" t="n"/>
+      <c r="AA4" s="28" t="n"/>
+      <c r="AB4" s="28" t="n"/>
+      <c r="AC4" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:57:21.360328Z</t>
+        </is>
+      </c>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-valorant-srg-swim-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG4" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH4" s="24" t="n"/>
+      <c r="AI4" s="31" t="n"/>
+      <c r="AJ4" s="31" t="n"/>
+      <c r="AK4" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN4" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO4" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP4" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AQ4" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AR4" s="24" t="inlineStr">
+        <is>
+          <t>SwimTrek Blue</t>
+        </is>
+      </c>
+      <c r="AS4" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Gold</t>
+        </is>
+      </c>
+      <c r="AT4" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Gold</t>
+        </is>
+      </c>
+      <c r="AU4" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion Gold</t>
+        </is>
+      </c>
+      <c r="AV4" s="24" t="n"/>
+      <c r="AW4" s="24" t="n"/>
+      <c r="AX4" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY4" s="24" t="n"/>
+      <c r="AZ4" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA4" s="24" t="inlineStr">
+        <is>
+          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+        </is>
+      </c>
+      <c r="BB4" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC4" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD4" s="24" t="inlineStr">
+        <is>
+          <t>781631928725bfbadab6eb37728b264ebd9b45792fc91e595051fe0740ec1b11</t>
+        </is>
+      </c>
+      <c r="BE4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG4" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH4" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:51:34.644041Z</t>
+        </is>
+      </c>
+      <c r="BI4" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ4" s="25" t="n"/>
+      <c r="BK4" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL4" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM4" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN4" s="28" t="n"/>
+      <c r="BO4" s="28" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
+      <c r="BR4" s="28" t="n"/>
+      <c r="BS4" s="28" t="n"/>
+      <c r="BT4" s="28" t="n"/>
+      <c r="BU4" s="25" t="n"/>
+      <c r="BV4" s="29" t="n"/>
+      <c r="BW4" s="24" t="n"/>
+      <c r="BX4" s="30" t="n"/>
+      <c r="BY4" s="27" t="n"/>
+      <c r="BZ4" s="24" t="n"/>
+      <c r="CA4" s="31" t="n"/>
+      <c r="CB4" s="24" t="n"/>
+      <c r="CC4" s="24" t="n"/>
+      <c r="CD4" s="24" t="n"/>
+      <c r="CE4" s="24" t="n"/>
+      <c r="CF4" s="24" t="n"/>
+      <c r="CG4" s="24" t="n"/>
+      <c r="CH4" s="24" t="n"/>
+      <c r="CI4" s="24" t="n"/>
+      <c r="CJ4" s="24" t="n"/>
+      <c r="CK4" s="24" t="n"/>
+      <c r="CL4" s="24" t="n"/>
+      <c r="CM4" s="24" t="n"/>
+      <c r="CN4" s="24" t="n"/>
+      <c r="CO4" s="24" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>5688484986ad45e4</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:56:56.096115Z</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>61239</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Los Chudeles</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L5" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N5" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="O5" s="28" t="n">
+        <v>0.557051</v>
+      </c>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="28" t="n">
+        <v>0.247453</v>
+      </c>
+      <c r="R5" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S5" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U5" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="26" t="n"/>
+      <c r="AA5" s="28" t="n"/>
+      <c r="AB5" s="28" t="n"/>
+      <c r="AC5" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:57:22.550923Z</t>
+        </is>
+      </c>
+      <c r="AE5" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-valorant-efa-lcd-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF5" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG5" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH5" s="24" t="n"/>
+      <c r="AI5" s="31" t="n"/>
+      <c r="AJ5" s="31" t="n"/>
+      <c r="AK5" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN5" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO5" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP5" s="24" t="inlineStr">
+        <is>
+          <t>Los Chudeles</t>
+        </is>
+      </c>
+      <c r="AQ5" s="24" t="inlineStr">
+        <is>
+          <t>Los Chudeles</t>
+        </is>
+      </c>
+      <c r="AR5" s="24" t="inlineStr">
+        <is>
+          <t>Los Chudeles</t>
+        </is>
+      </c>
+      <c r="AS5" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="AT5" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="AU5" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Focus Amethyst</t>
+        </is>
+      </c>
+      <c r="AV5" s="24" t="n"/>
+      <c r="AW5" s="24" t="n"/>
+      <c r="AX5" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY5" s="24" t="n"/>
+      <c r="AZ5" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA5" s="24" t="inlineStr">
+        <is>
+          <t>e1ac23d99e831b81cddfe7dc2c7cc5dd4b57a35e88319d1f7162fbb6350e11bd</t>
+        </is>
+      </c>
+      <c r="BB5" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC5" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD5" s="24" t="inlineStr">
+        <is>
+          <t>e1ac23d99e831b81cddfe7dc2c7cc5dd4b57a35e88319d1f7162fbb6350e11bd</t>
+        </is>
+      </c>
+      <c r="BE5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG5" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH5" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:56:51.769330Z</t>
+        </is>
+      </c>
+      <c r="BI5" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ5" s="25" t="n"/>
+      <c r="BK5" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="BL5" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BM5" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="BN5" s="28" t="n"/>
+      <c r="BO5" s="28" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
+      <c r="BR5" s="28" t="n"/>
+      <c r="BS5" s="28" t="n"/>
+      <c r="BT5" s="28" t="n"/>
+      <c r="BU5" s="25" t="n"/>
+      <c r="BV5" s="29" t="n"/>
+      <c r="BW5" s="24" t="n"/>
+      <c r="BX5" s="30" t="n"/>
+      <c r="BY5" s="27" t="n"/>
+      <c r="BZ5" s="24" t="n"/>
+      <c r="CA5" s="31" t="n"/>
+      <c r="CB5" s="24" t="n"/>
+      <c r="CC5" s="24" t="n"/>
+      <c r="CD5" s="24" t="n"/>
+      <c r="CE5" s="24" t="n"/>
+      <c r="CF5" s="24" t="n"/>
+      <c r="CG5" s="24" t="n"/>
+      <c r="CH5" s="24" t="n"/>
+      <c r="CI5" s="24" t="n"/>
+      <c r="CJ5" s="24" t="n"/>
+      <c r="CK5" s="24" t="n"/>
+      <c r="CL5" s="24" t="n"/>
+      <c r="CM5" s="24" t="n"/>
+      <c r="CN5" s="24" t="n"/>
+      <c r="CO5" s="24" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>b5755573ea37414d</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:56:56.096115Z</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>61240</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Revenge</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>:3</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="O6" s="28" t="n">
+        <v>0.500347</v>
+      </c>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="28" t="n">
+        <v>0.190749</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S6" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U6" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="25" t="n"/>
+      <c r="Z6" s="26" t="n"/>
+      <c r="AA6" s="28" t="n"/>
+      <c r="AB6" s="28" t="n"/>
+      <c r="AC6" s="30" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:57:23.798044Z</t>
+        </is>
+      </c>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-valorant-meow-rvn-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG6" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH6" s="24" t="n"/>
+      <c r="AI6" s="31" t="n"/>
+      <c r="AJ6" s="31" t="n"/>
+      <c r="AK6" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN6" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP6" s="24" t="inlineStr">
+        <is>
+          <t>Revenge</t>
+        </is>
+      </c>
+      <c r="AQ6" s="24" t="inlineStr">
+        <is>
+          <t>Revenge</t>
+        </is>
+      </c>
+      <c r="AR6" s="24" t="inlineStr">
+        <is>
+          <t>Revenge</t>
+        </is>
+      </c>
+      <c r="AS6" s="24" t="inlineStr">
+        <is>
+          <t>:3</t>
+        </is>
+      </c>
+      <c r="AT6" s="24" t="inlineStr">
+        <is>
+          <t>:3</t>
+        </is>
+      </c>
+      <c r="AU6" s="24" t="inlineStr">
+        <is>
+          <t>:3</t>
+        </is>
+      </c>
+      <c r="AV6" s="24" t="n"/>
+      <c r="AW6" s="24" t="n"/>
+      <c r="AX6" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY6" s="24" t="n"/>
+      <c r="AZ6" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA6" s="24" t="inlineStr">
+        <is>
+          <t>e1ac23d99e831b81cddfe7dc2c7cc5dd4b57a35e88319d1f7162fbb6350e11bd</t>
+        </is>
+      </c>
+      <c r="BB6" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD6" s="24" t="inlineStr">
+        <is>
+          <t>e1ac23d99e831b81cddfe7dc2c7cc5dd4b57a35e88319d1f7162fbb6350e11bd</t>
+        </is>
+      </c>
+      <c r="BE6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH6" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:56:52.318174Z</t>
+        </is>
+      </c>
+      <c r="BI6" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ6" s="25" t="n"/>
+      <c r="BK6" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="BL6" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BM6" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="BN6" s="28" t="n"/>
+      <c r="BO6" s="28" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
+      <c r="BR6" s="28" t="n"/>
+      <c r="BS6" s="28" t="n"/>
+      <c r="BT6" s="28" t="n"/>
+      <c r="BU6" s="25" t="n"/>
+      <c r="BV6" s="29" t="n"/>
+      <c r="BW6" s="24" t="n"/>
+      <c r="BX6" s="30" t="n"/>
+      <c r="BY6" s="27" t="n"/>
+      <c r="BZ6" s="24" t="n"/>
+      <c r="CA6" s="31" t="n"/>
+      <c r="CB6" s="24" t="n"/>
+      <c r="CC6" s="24" t="n"/>
+      <c r="CD6" s="24" t="n"/>
+      <c r="CE6" s="24" t="n"/>
+      <c r="CF6" s="24" t="n"/>
+      <c r="CG6" s="24" t="n"/>
+      <c r="CH6" s="24" t="n"/>
+      <c r="CI6" s="24" t="n"/>
+      <c r="CJ6" s="24" t="n"/>
+      <c r="CK6" s="24" t="n"/>
+      <c r="CL6" s="24" t="n"/>
+      <c r="CM6" s="24" t="n"/>
+      <c r="CN6" s="24" t="n"/>
+      <c r="CO6" s="24" t="n"/>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>96c3a75d32bc4595</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:16.375053Z</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>61529</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N7" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O7" s="28" t="n">
+        <v>0.528676</v>
+      </c>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="28" t="n">
+        <v>0.067847</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <v>54</v>
+      </c>
+      <c r="S7" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="n"/>
+      <c r="W7" s="26" t="n"/>
+      <c r="X7" s="26" t="n"/>
+      <c r="Y7" s="25" t="n"/>
+      <c r="Z7" s="26" t="n"/>
+      <c r="AA7" s="28" t="n"/>
+      <c r="AB7" s="28" t="n"/>
+      <c r="AC7" s="30" t="n"/>
+      <c r="AD7" s="24" t="n"/>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-beg-kcg-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG7" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH7" s="24" t="n"/>
+      <c r="AI7" s="31" t="n"/>
+      <c r="AJ7" s="31" t="n"/>
+      <c r="AK7" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN7" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO7" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP7" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AQ7" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AR7" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp GC</t>
+        </is>
+      </c>
+      <c r="AS7" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="AT7" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="AU7" s="24" t="inlineStr">
+        <is>
+          <t>Barça eSports GC</t>
+        </is>
+      </c>
+      <c r="AV7" s="24" t="n"/>
+      <c r="AW7" s="24" t="n"/>
+      <c r="AX7" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY7" s="24" t="n"/>
+      <c r="AZ7" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA7" s="24" t="inlineStr">
+        <is>
+          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
+        </is>
+      </c>
+      <c r="BB7" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC7" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD7" s="24" t="inlineStr">
+        <is>
+          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
+        </is>
+      </c>
+      <c r="BE7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG7" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:13.741488Z</t>
+        </is>
+      </c>
+      <c r="BI7" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ7" s="25" t="n"/>
+      <c r="BK7" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL7" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM7" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN7" s="28" t="n"/>
+      <c r="BO7" s="28" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
+      <c r="BR7" s="28" t="n"/>
+      <c r="BS7" s="28" t="n"/>
+      <c r="BT7" s="28" t="n"/>
+      <c r="BU7" s="25" t="n"/>
+      <c r="BV7" s="29" t="n"/>
+      <c r="BW7" s="24" t="n"/>
+      <c r="BX7" s="30" t="n"/>
+      <c r="BY7" s="27" t="n"/>
+      <c r="BZ7" s="24" t="n"/>
+      <c r="CA7" s="31" t="n"/>
+      <c r="CB7" s="24" t="n"/>
+      <c r="CC7" s="24" t="n"/>
+      <c r="CD7" s="24" t="n"/>
+      <c r="CE7" s="24" t="n"/>
+      <c r="CF7" s="24" t="n"/>
+      <c r="CG7" s="24" t="n"/>
+      <c r="CH7" s="24" t="n"/>
+      <c r="CI7" s="24" t="n"/>
+      <c r="CJ7" s="24" t="n"/>
+      <c r="CK7" s="24" t="n"/>
+      <c r="CL7" s="24" t="n"/>
+      <c r="CM7" s="24" t="n"/>
+      <c r="CN7" s="24" t="n"/>
+      <c r="CO7" s="24" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>f4bf5979bd4949af</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:16.375053Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>61735</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.619109</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>0.028945</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="n"/>
+      <c r="W8" s="26" t="n"/>
+      <c r="X8" s="26" t="n"/>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n"/>
+      <c r="AD8" s="24" t="n"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-valorant-tmo-hbs-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>Habos Babos</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>Twisted Minds Orchid</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:15.790363Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN8" s="28" t="n"/>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+      <c r="CB8" s="24" t="n"/>
+      <c r="CC8" s="24" t="n"/>
+      <c r="CD8" s="24" t="n"/>
+      <c r="CE8" s="24" t="n"/>
+      <c r="CF8" s="24" t="n"/>
+      <c r="CG8" s="24" t="n"/>
+      <c r="CH8" s="24" t="n"/>
+      <c r="CI8" s="24" t="n"/>
+      <c r="CJ8" s="24" t="n"/>
+      <c r="CK8" s="24" t="n"/>
+      <c r="CL8" s="24" t="n"/>
+      <c r="CM8" s="24" t="n"/>
+      <c r="CN8" s="24" t="n"/>
+      <c r="CO8" s="24" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:CO1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO8" headerRowCount="1">
-  <autoFilter ref="A1:CO8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO7" headerRowCount="1">
+  <autoFilter ref="A1:CO7"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$8)</f>
+        <f>COUNTA('Picks'!$A$2:$A$7)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$8,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$7,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$8,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$7,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")/(COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"win")+COUNTIFS('Picks'!$BX$2:$BX$8,"&gt;0",'Picks'!$V$2:$V$8,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")/(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$8)/SUM('Picks'!$BX$2:$BX$8),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$7)/SUM('Picks'!$BX$2:$BX$7),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$8)</f>
+        <f>SUM('Picks'!$BY$2:$BY$7)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$8,"&lt;&gt;",'Picks'!$AB$2:$AB$8),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$7,"&lt;&gt;",'Picks'!$AB$2:$AB$7),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$8,'Picks'!$AM$2:$AM$8,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$7,'Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A14,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A15,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled",'Picks'!$V$2:$V$8,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$8,'Picks'!$H$2:$H$8,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$8,'Picks'!$H$2:$H$8,$A16,'Picks'!$U$2:$U$8,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO8"/>
+  <dimension ref="A1:CO7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2953,12 +2953,12 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>96c3a75d32bc4595</t>
+          <t>eaaad94fb2a84761</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:16.375053Z</t>
+          <t>2026-07-28T14:24:30.873029Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
@@ -3003,23 +3003,23 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.420168</v>
       </c>
       <c r="O7" s="28" t="n">
         <v>0.528676</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.067847</v>
+        <v>0.108508</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="S7" s="29" t="n">
         <v>0.75</v>
@@ -3045,7 +3045,7 @@
       <c r="AD7" s="24" t="n"/>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-beg-kcg-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-beg-kcg-2026-07-28).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
+          <t>cee841572684572d854c56b6d6e919489ee19e082da259a5e2f60f76864ab64f</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
+          <t>cee841572684572d854c56b6d6e919489ee19e082da259a5e2f60f76864ab64f</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:13.741488Z</t>
+          <t>2026-07-28T14:24:24.591584Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3174,13 +3174,13 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.420168</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
@@ -3211,267 +3211,6 @@
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
     </row>
-    <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>f4bf5979bd4949af</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:16.375053Z</t>
-        </is>
-      </c>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
-        <is>
-          <t>61735</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F8" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="G8" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I8" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J8" s="25" t="n"/>
-      <c r="K8" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L8" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="M8" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="N8" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="O8" s="28" t="n">
-        <v>0.619109</v>
-      </c>
-      <c r="P8" s="28" t="n"/>
-      <c r="Q8" s="28" t="n">
-        <v>0.028945</v>
-      </c>
-      <c r="R8" s="26" t="n">
-        <v>34</v>
-      </c>
-      <c r="S8" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T8" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U8" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
-      <c r="Y8" s="25" t="n"/>
-      <c r="Z8" s="26" t="n"/>
-      <c r="AA8" s="28" t="n"/>
-      <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
-      <c r="AE8" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-valorant-tmo-hbs-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF8" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG8" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH8" s="24" t="n"/>
-      <c r="AI8" s="31" t="n"/>
-      <c r="AJ8" s="31" t="n"/>
-      <c r="AK8" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL8" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM8" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN8" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO8" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP8" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="AQ8" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="AR8" s="24" t="inlineStr">
-        <is>
-          <t>Habos Babos</t>
-        </is>
-      </c>
-      <c r="AS8" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="AT8" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="AU8" s="24" t="inlineStr">
-        <is>
-          <t>Twisted Minds Orchid</t>
-        </is>
-      </c>
-      <c r="AV8" s="24" t="n"/>
-      <c r="AW8" s="24" t="n"/>
-      <c r="AX8" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY8" s="24" t="n"/>
-      <c r="AZ8" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA8" s="24" t="inlineStr">
-        <is>
-          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
-        </is>
-      </c>
-      <c r="BB8" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC8" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD8" s="24" t="inlineStr">
-        <is>
-          <t>ba99965c8114221fba78930616e91bad6782222f73e86a28a2f2985fae341dcb</t>
-        </is>
-      </c>
-      <c r="BE8" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF8" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG8" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH8" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:15.790363Z</t>
-        </is>
-      </c>
-      <c r="BI8" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ8" s="25" t="n"/>
-      <c r="BK8" s="26" t="n">
-        <v>-144</v>
-      </c>
-      <c r="BL8" s="27" t="n">
-        <v>1.694444</v>
-      </c>
-      <c r="BM8" s="28" t="n">
-        <v>0.590164</v>
-      </c>
-      <c r="BN8" s="28" t="n"/>
-      <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
-      <c r="BR8" s="28" t="n"/>
-      <c r="BS8" s="28" t="n"/>
-      <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="25" t="n"/>
-      <c r="BV8" s="29" t="n"/>
-      <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n"/>
-      <c r="BY8" s="27" t="n"/>
-      <c r="BZ8" s="24" t="n"/>
-      <c r="CA8" s="31" t="n"/>
-      <c r="CB8" s="24" t="n"/>
-      <c r="CC8" s="24" t="n"/>
-      <c r="CD8" s="24" t="n"/>
-      <c r="CE8" s="24" t="n"/>
-      <c r="CF8" s="24" t="n"/>
-      <c r="CG8" s="24" t="n"/>
-      <c r="CH8" s="24" t="n"/>
-      <c r="CI8" s="24" t="n"/>
-      <c r="CJ8" s="24" t="n"/>
-      <c r="CK8" s="24" t="n"/>
-      <c r="CL8" s="24" t="n"/>
-      <c r="CM8" s="24" t="n"/>
-      <c r="CN8" s="24" t="n"/>
-      <c r="CO8" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO7" headerRowCount="1">
-  <autoFilter ref="A1:CO7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO13" headerRowCount="1">
+  <autoFilter ref="A1:CO13"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$7)</f>
+        <f>COUNTA('Picks'!$A$2:$A$13)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$7,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$13,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$7,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$13,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")/(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")/(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$7)/SUM('Picks'!$BX$2:$BX$7),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$13)/SUM('Picks'!$BX$2:$BX$13),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$7)</f>
+        <f>SUM('Picks'!$BY$2:$BY$13)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$7,"&lt;&gt;",'Picks'!$AB$2:$AB$7),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$13,"&lt;&gt;",'Picks'!$AB$2:$AB$13),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$7,'Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$13,'Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO7"/>
+  <dimension ref="A1:CO13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3031,18 +3031,32 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="AC7" s="30" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T20:31:39.099946Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-beg-kcg-2026-07-28).</t>
@@ -3055,7 +3069,7 @@
       </c>
       <c r="AG7" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH7" s="24" t="n"/>
@@ -3211,6 +3225,1600 @@
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
     </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>72744ff7477e4102</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T12:04:22.575418Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>62689</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>G2 Gozen</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.714884</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>0.234115</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:34:59.328852Z</t>
+        </is>
+      </c>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-valorant-skn-ggo-2026-07-29).</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>G2 Gozen</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>G2 Gozen</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>G2 Gozen</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>e33860310416f9b2d86e5c1e14a7bffcebc7a1e4c8af04b416cd37235fd4b6cf</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>e33860310416f9b2d86e5c1e14a7bffcebc7a1e4c8af04b416cd37235fd4b6cf</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T12:04:15.273824Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN8" s="28" t="n"/>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+      <c r="CB8" s="24" t="n"/>
+      <c r="CC8" s="24" t="n"/>
+      <c r="CD8" s="24" t="n"/>
+      <c r="CE8" s="24" t="n"/>
+      <c r="CF8" s="24" t="n"/>
+      <c r="CG8" s="24" t="n"/>
+      <c r="CH8" s="24" t="n"/>
+      <c r="CI8" s="24" t="n"/>
+      <c r="CJ8" s="24" t="n"/>
+      <c r="CK8" s="24" t="n"/>
+      <c r="CL8" s="24" t="n"/>
+      <c r="CM8" s="24" t="n"/>
+      <c r="CN8" s="24" t="n"/>
+      <c r="CO8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>d80f3f8619e24310</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:48:33.149264Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>64563</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.827349</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.127649</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-valorant-100t-sen-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>Sentinels</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>100 Thieves</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>71696e637dd05bc7933e2bdcf627a39cf9f10c85a7ad852765447d083e849a9e</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>71696e637dd05bc7933e2bdcf627a39cf9f10c85a7ad852765447d083e849a9e</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-29T17:48:33.146517Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>87c76c65bfd54872</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:24:48.854145Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>63626</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>DetonatioN FocusMe</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>VARREL</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.604202</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>0.02437</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T13:31:06.600054Z</t>
+        </is>
+      </c>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-valorant-var-dfm-2026-07-30).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>DetonatioN FocusMe</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>DetonatioN FocusMe</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>DetonatioN FocusMe</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>VARREL</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>VARREL</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>VARREL</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>065060c5427d777daf1c2c539c66a4917e7e7a09bf311e9c39e713455cc3d93a</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>065060c5427d777daf1c2c539c66a4917e7e7a09bf311e9c39e713455cc3d93a</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T07:24:41.203557Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>ef6e12da16724928</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:19.984320Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>64807</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Global Esports</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.581239</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.062008</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-valorant-ge-geng-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Global Esports</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Global Esports</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Global Esports</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:17.979503Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>43b7e6a3dd07450b</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:19.984320Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>64940</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>BBL Esports</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.603976</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>0.044505</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>42</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="26" t="n"/>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n"/>
+      <c r="AD12" s="24" t="n"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-valorant-bbl-gm-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>BBL Esports</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>BBL Esports</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>BBL Esports</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:18.461860Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>a7048cef071c4f94</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:19.984320Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>65506</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.648906</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.109735</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-valorant-c9-loud-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:56:19.463536Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -4039,12 +4039,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>ef6e12da16724928</t>
+          <t>7651315953934b37</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:19.984320Z</t>
+          <t>2026-07-30T17:22:29.306490Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4098,11 +4098,11 @@
         <v>0.519231</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.581239</v>
+        <v>0.581533</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.062008</v>
+        <v>0.062302</v>
       </c>
       <c r="R11" s="26" t="n">
         <v>51</v>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:17.979503Z</t>
+          <t>2026-07-30T17:22:27.119043Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4300,12 +4300,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>43b7e6a3dd07450b</t>
+          <t>5d473d1014c7436d</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:19.984320Z</t>
+          <t>2026-07-30T17:22:29.306490Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4359,11 +4359,11 @@
         <v>0.5594710000000001</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.603976</v>
+        <v>0.6034080000000001</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.044505</v>
+        <v>0.043937</v>
       </c>
       <c r="R12" s="26" t="n">
         <v>42</v>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:18.461860Z</t>
+          <t>2026-07-30T17:22:27.586615Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4561,12 +4561,12 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>a7048cef071c4f94</t>
+          <t>3a794099d03e4f97</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:19.984320Z</t>
+          <t>2026-07-30T17:22:29.306490Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
@@ -4620,11 +4620,11 @@
         <v>0.539171</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.648906</v>
+        <v>0.649081</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.109735</v>
+        <v>0.10991</v>
       </c>
       <c r="R13" s="26" t="n">
         <v>75</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>35b04a5bb7c454d67f676c74c39ff026dc1de3ca4c28121046d47414d56b3caf</t>
+          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:56:19.463536Z</t>
+          <t>2026-07-30T17:22:28.738967Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO13" headerRowCount="1">
-  <autoFilter ref="A1:CO13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO15" headerRowCount="1">
+  <autoFilter ref="A1:CO15"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$13)</f>
+        <f>COUNTA('Picks'!$A$2:$A$15)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$13,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$13,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")/(COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"win")+COUNTIFS('Picks'!$BX$2:$BX$13,"&gt;0",'Picks'!$V$2:$V$13,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$13)/SUM('Picks'!$BX$2:$BX$13),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$13)</f>
+        <f>SUM('Picks'!$BY$2:$BY$15)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$13,"&lt;&gt;",'Picks'!$AB$2:$AB$13),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$13,'Picks'!$AM$2:$AM$13,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A14,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A15,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled",'Picks'!$V$2:$V$13,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$13,'Picks'!$H$2:$H$13,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$13,'Picks'!$H$2:$H$13,$A16,'Picks'!$U$2:$U$13,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO13"/>
+  <dimension ref="A1:CO15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4039,22 +4039,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>7651315953934b37</t>
+          <t>c24b9ea80a1147d3</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:29.306490Z</t>
+          <t>2026-07-30T17:40:05.919152Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T11:00:00Z</t>
+          <t>2026-07-30T18:00:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>64807</t>
+          <t>64031</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>Eternal Fire</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4089,26 +4089,26 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>-108</v>
+        <v>-122</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.819672</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.54955</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.581533</v>
+        <v>0.645947</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.062302</v>
+        <v>0.096397</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="S11" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T11" s="24" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
       <c r="AD11" s="24" t="n"/>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-valorant-ge-geng-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-valorant-ef-fnc-2026-07-30).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4172,32 +4172,32 @@
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>Eternal Fire</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>Eternal Fire</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>Eternal Fire</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:27.119043Z</t>
+          <t>2026-07-30T17:40:01.228013Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4260,13 +4260,13 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>-108</v>
+        <v>-122</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.819672</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.54955</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
@@ -4300,22 +4300,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>5d473d1014c7436d</t>
+          <t>17b5f6d4bae94e2e</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:29.306490Z</t>
+          <t>2026-07-30T17:40:05.919152Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T15:00:00Z</t>
+          <t>2026-07-30T18:00:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>64940</t>
+          <t>64028</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>G2 Gozen</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4350,26 +4350,26 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-127</v>
+        <v>127</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.27</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.440529</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.6034080000000001</v>
+        <v>0.6363760000000001</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.043937</v>
+        <v>0.195847</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
       <c r="AD12" s="24" t="n"/>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-valorant-bbl-gm-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-valorant-ggo-tmo-2026-07-30).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4433,32 +4433,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>G2 Gozen</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>G2 Gozen</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>G2 Gozen</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:27.586615Z</t>
+          <t>2026-07-30T17:40:01.726408Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4521,13 +4521,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-127</v>
+        <v>127</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.27</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.440529</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4561,22 +4561,22 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>3a794099d03e4f97</t>
+          <t>71c376b6b57a4948</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:29.306490Z</t>
+          <t>2026-07-30T17:40:05.919152Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T21:00:00Z</t>
+          <t>2026-07-31T11:00:00Z</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>65506</t>
+          <t>64807</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -4611,26 +4611,26 @@
         </is>
       </c>
       <c r="L13" s="26" t="n">
-        <v>-117</v>
+        <v>-108</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.925926</v>
       </c>
       <c r="N13" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.519231</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.649081</v>
+        <v>0.581533</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.10991</v>
+        <v>0.062302</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="S13" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T13" s="24" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
       <c r="AD13" s="24" t="n"/>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-valorant-c9-loud-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-valorant-ge-geng-2026-07-31).</t>
         </is>
       </c>
       <c r="AF13" s="31" t="inlineStr">
@@ -4694,32 +4694,32 @@
       </c>
       <c r="AP13" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AQ13" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AR13" s="24" t="inlineStr">
         <is>
-          <t>LOUD</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AS13" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="AT13" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="AU13" s="24" t="inlineStr">
         <is>
-          <t>Cloud9</t>
+          <t>Global Esports</t>
         </is>
       </c>
       <c r="AV13" s="24" t="n"/>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>bba2c330fac2df7607a39f9ef9e19f27107432ae9668acb570783f46498e4fd2</t>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:22:28.738967Z</t>
+          <t>2026-07-30T17:40:03.847842Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4782,13 +4782,13 @@
       </c>
       <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
-        <v>-117</v>
+        <v>-108</v>
       </c>
       <c r="BL13" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.925926</v>
       </c>
       <c r="BM13" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.519231</v>
       </c>
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
@@ -4819,6 +4819,528 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
     </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>a7e98f7b75854d3f</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:40:05.919152Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>64940</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>BBL Esports</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.6034080000000001</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>0.032593</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="n"/>
+      <c r="W14" s="26" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-valorant-bbl-gm-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>BBL Esports</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>BBL Esports</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>BBL Esports</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:40:04.331936Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>a24d133e14d04a03</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:40:05.919152Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>65506</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.649081</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.10991</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-valorant-c9-loud-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>LOUD</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>d0cfd58f4b00ffbf06b9629226e9ca0eeddd55588f9724c6a38af3b483750825</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:40:05.383273Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO5" headerRowCount="1">
-  <autoFilter ref="A1:CO5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO6" headerRowCount="1">
+  <autoFilter ref="A1:CO6"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$5)</f>
+        <f>COUNTA('Picks'!$A$2:$A$6)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$5,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$6,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")+COUNTIFS('Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$5,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$6,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")/(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")/(COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")+COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$5)/SUM('Picks'!$BX$2:$BX$5),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$6)/SUM('Picks'!$BX$2:$BX$6),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$5)</f>
+        <f>SUM('Picks'!$BY$2:$BY$6)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$5,"&lt;&gt;",'Picks'!$AB$2:$AB$5),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$6,"&lt;&gt;",'Picks'!$AB$2:$AB$6),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$6,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$5,'Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$6,'Picks'!$AM$2:$AM$6,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO5"/>
+  <dimension ref="A1:CO6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2148,22 +2148,22 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>e49cff1a4ca2408d</t>
+          <t>3ed05efb0fb74970</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:33:11.238423Z</t>
+          <t>2026-08-01T23:55:04.278999Z</t>
         </is>
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00Z</t>
+          <t>2026-08-02T00:00:00Z</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>67569</t>
+          <t>66659</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Leviatán Esports</t>
         </is>
       </c>
       <c r="H4" s="24" t="inlineStr">
@@ -2198,26 +2198,26 @@
         </is>
       </c>
       <c r="L4" s="26" t="n">
-        <v>-203</v>
+        <v>-138</v>
       </c>
       <c r="M4" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.724638</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.579832</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>0.76553</v>
+        <v>0.608104</v>
       </c>
       <c r="P4" s="28" t="n"/>
       <c r="Q4" s="28" t="n">
-        <v>0.095563</v>
+        <v>0.028272</v>
       </c>
       <c r="R4" s="26" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="S4" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T4" s="24" t="inlineStr">
         <is>
@@ -2226,21 +2226,41 @@
       </c>
       <c r="U4" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V4" s="24" t="n"/>
-      <c r="W4" s="26" t="n"/>
-      <c r="X4" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W4" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y4" s="25" t="n"/>
-      <c r="Z4" s="26" t="n"/>
-      <c r="AA4" s="28" t="n"/>
-      <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="30" t="n"/>
-      <c r="AD4" s="24" t="n"/>
+      <c r="Z4" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="AA4" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB4" s="28" t="n">
+        <v>0.000168</v>
+      </c>
+      <c r="AC4" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD4" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T04:26:24.624792Z</t>
+        </is>
+      </c>
       <c r="AE4" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-valorant-lev-nrg-2026-08-02).</t>
         </is>
       </c>
       <c r="AF4" s="31" t="inlineStr">
@@ -2250,7 +2270,7 @@
       </c>
       <c r="AG4" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH4" s="24" t="n"/>
@@ -2281,32 +2301,32 @@
       </c>
       <c r="AP4" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="AQ4" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="AR4" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="AS4" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Leviatán Esports</t>
         </is>
       </c>
       <c r="AT4" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Leviatán Esports</t>
         </is>
       </c>
       <c r="AU4" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Leviatán Esports</t>
         </is>
       </c>
       <c r="AV4" s="24" t="n"/>
@@ -2324,7 +2344,7 @@
       </c>
       <c r="BA4" s="24" t="inlineStr">
         <is>
-          <t>6c2fe30bde2e3d49744e134c7d83a04f47b0437d09b6f8743e0023be67965171</t>
+          <t>4e9833fa3108f9876de728871233bbb749924096e4b6984ae7ee11ff9d8be0d1</t>
         </is>
       </c>
       <c r="BB4" s="24" t="inlineStr">
@@ -2339,7 +2359,7 @@
       </c>
       <c r="BD4" s="24" t="inlineStr">
         <is>
-          <t>6c2fe30bde2e3d49744e134c7d83a04f47b0437d09b6f8743e0023be67965171</t>
+          <t>4e9833fa3108f9876de728871233bbb749924096e4b6984ae7ee11ff9d8be0d1</t>
         </is>
       </c>
       <c r="BE4" s="24" t="inlineStr">
@@ -2359,7 +2379,7 @@
       </c>
       <c r="BH4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:33:06.494162Z</t>
+          <t>2026-08-01T23:55:01.262855Z</t>
         </is>
       </c>
       <c r="BI4" s="24" t="inlineStr">
@@ -2369,19 +2389,23 @@
       </c>
       <c r="BJ4" s="25" t="n"/>
       <c r="BK4" s="26" t="n">
-        <v>-203</v>
+        <v>-138</v>
       </c>
       <c r="BL4" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.724638</v>
       </c>
       <c r="BM4" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.579832</v>
       </c>
       <c r="BN4" s="28" t="n"/>
       <c r="BO4" s="28" t="n"/>
       <c r="BP4" s="25" t="n"/>
-      <c r="BQ4" s="27" t="n"/>
-      <c r="BR4" s="28" t="n"/>
+      <c r="BQ4" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BR4" s="28" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
       <c r="BU4" s="25" t="n"/>
@@ -2409,12 +2433,12 @@
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>0820e7d805e7451f</t>
+          <t>9be1b88469434301</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:40.423686Z</t>
+          <t>2026-08-02T07:16:42.752833Z</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
@@ -2459,23 +2483,23 @@
         </is>
       </c>
       <c r="L5" s="26" t="n">
-        <v>-138</v>
+        <v>-150</v>
       </c>
       <c r="M5" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.666667</v>
       </c>
       <c r="N5" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.6</v>
       </c>
       <c r="O5" s="28" t="n">
-        <v>0.677597</v>
+        <v>0.676998</v>
       </c>
       <c r="P5" s="28" t="n"/>
       <c r="Q5" s="28" t="n">
-        <v>0.097765</v>
+        <v>0.076998</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="S5" s="29" t="n">
         <v>1.75</v>
@@ -2501,7 +2525,7 @@
       <c r="AD5" s="24" t="n"/>
       <c r="AE5" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-valorant-var-krx-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-valorant-var-krx-2026-08-02).</t>
         </is>
       </c>
       <c r="AF5" s="31" t="inlineStr">
@@ -2585,7 +2609,7 @@
       </c>
       <c r="BA5" s="24" t="inlineStr">
         <is>
-          <t>3d9fb2e99557b8380ebae212c50f062d30d580c0a2a0d2fab1fc8860b2260810</t>
+          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
         </is>
       </c>
       <c r="BB5" s="24" t="inlineStr">
@@ -2600,7 +2624,7 @@
       </c>
       <c r="BD5" s="24" t="inlineStr">
         <is>
-          <t>3d9fb2e99557b8380ebae212c50f062d30d580c0a2a0d2fab1fc8860b2260810</t>
+          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
         </is>
       </c>
       <c r="BE5" s="24" t="inlineStr">
@@ -2620,7 +2644,7 @@
       </c>
       <c r="BH5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:32.281041Z</t>
+          <t>2026-08-02T07:16:34.729300Z</t>
         </is>
       </c>
       <c r="BI5" s="24" t="inlineStr">
@@ -2630,13 +2654,13 @@
       </c>
       <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
-        <v>-138</v>
+        <v>-150</v>
       </c>
       <c r="BL5" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.666667</v>
       </c>
       <c r="BM5" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.6</v>
       </c>
       <c r="BN5" s="28" t="n"/>
       <c r="BO5" s="28" t="n"/>
@@ -2667,6 +2691,267 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
     </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>1502c6ab3b034c48</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:42.752833Z</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="O6" s="28" t="n">
+        <v>0.765271</v>
+      </c>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="28" t="n">
+        <v>0.08476</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S6" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U6" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="n"/>
+      <c r="W6" s="26" t="n"/>
+      <c r="X6" s="26" t="n"/>
+      <c r="Y6" s="25" t="n"/>
+      <c r="Z6" s="26" t="n"/>
+      <c r="AA6" s="28" t="n"/>
+      <c r="AB6" s="28" t="n"/>
+      <c r="AC6" s="30" t="n"/>
+      <c r="AD6" s="24" t="n"/>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG6" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH6" s="24" t="n"/>
+      <c r="AI6" s="31" t="n"/>
+      <c r="AJ6" s="31" t="n"/>
+      <c r="AK6" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN6" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP6" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AQ6" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AR6" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AS6" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AT6" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AU6" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AV6" s="24" t="n"/>
+      <c r="AW6" s="24" t="n"/>
+      <c r="AX6" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY6" s="24" t="n"/>
+      <c r="AZ6" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA6" s="24" t="inlineStr">
+        <is>
+          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+        </is>
+      </c>
+      <c r="BB6" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD6" s="24" t="inlineStr">
+        <is>
+          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+        </is>
+      </c>
+      <c r="BE6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:38.239558Z</t>
+        </is>
+      </c>
+      <c r="BI6" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ6" s="25" t="n"/>
+      <c r="BK6" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="BL6" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BM6" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="BN6" s="28" t="n"/>
+      <c r="BO6" s="28" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
+      <c r="BR6" s="28" t="n"/>
+      <c r="BS6" s="28" t="n"/>
+      <c r="BT6" s="28" t="n"/>
+      <c r="BU6" s="25" t="n"/>
+      <c r="BV6" s="29" t="n"/>
+      <c r="BW6" s="24" t="n"/>
+      <c r="BX6" s="30" t="n"/>
+      <c r="BY6" s="27" t="n"/>
+      <c r="BZ6" s="24" t="n"/>
+      <c r="CA6" s="31" t="n"/>
+      <c r="CB6" s="24" t="n"/>
+      <c r="CC6" s="24" t="n"/>
+      <c r="CD6" s="24" t="n"/>
+      <c r="CE6" s="24" t="n"/>
+      <c r="CF6" s="24" t="n"/>
+      <c r="CG6" s="24" t="n"/>
+      <c r="CH6" s="24" t="n"/>
+      <c r="CI6" s="24" t="n"/>
+      <c r="CJ6" s="24" t="n"/>
+      <c r="CK6" s="24" t="n"/>
+      <c r="CL6" s="24" t="n"/>
+      <c r="CM6" s="24" t="n"/>
+      <c r="CN6" s="24" t="n"/>
+      <c r="CO6" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -2694,12 +2694,12 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>1502c6ab3b034c48</t>
+          <t>5681cf4218844f9a</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:42.752833Z</t>
+          <t>2026-08-02T08:19:54.418500Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:38.239558Z</t>
+          <t>2026-08-02T08:19:49.952914Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -2694,12 +2694,12 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>5681cf4218844f9a</t>
+          <t>bf114af371174342</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:54.418500Z</t>
+          <t>2026-08-02T10:00:21.466032Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
+          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>4b06d4c8598c61f9c6a8d114844ea0a58ae02951d130930c6509d4190167697d</t>
+          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:49.952914Z</t>
+          <t>2026-08-02T10:00:16.849872Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO6" headerRowCount="1">
-  <autoFilter ref="A1:CO6"/>
-  <tableColumns count="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP6" headerRowCount="1">
+  <autoFilter ref="A1:CP6"/>
+  <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,6 +396,7 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
+    <tableColumn id="94" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1010,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO6"/>
+  <dimension ref="A1:CP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1107,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1572,6 +1574,11 @@
       <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
+        </is>
+      </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
         </is>
       </c>
     </row>
@@ -1859,6 +1866,7 @@
       <c r="CM2" s="24" t="n"/>
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2144,6 +2152,7 @@
       <c r="CM3" s="24" t="n"/>
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2429,6 +2438,7 @@
       <c r="CM4" s="24" t="n"/>
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
+      <c r="CP4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2511,18 +2521,38 @@
       </c>
       <c r="U5" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V5" s="24" t="n"/>
-      <c r="W5" s="26" t="n"/>
-      <c r="X5" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y5" s="25" t="n"/>
-      <c r="Z5" s="26" t="n"/>
-      <c r="AA5" s="28" t="n"/>
-      <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="24" t="n"/>
+      <c r="Z5" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="AA5" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB5" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T11:45:35.969857Z</t>
+        </is>
+      </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-valorant-var-krx-2026-08-02).</t>
@@ -2535,7 +2565,7 @@
       </c>
       <c r="AG5" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH5" s="24" t="n"/>
@@ -2665,8 +2695,12 @@
       <c r="BN5" s="28" t="n"/>
       <c r="BO5" s="28" t="n"/>
       <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n"/>
-      <c r="BR5" s="28" t="n"/>
+      <c r="BQ5" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BR5" s="28" t="n">
+        <v>0.6</v>
+      </c>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
       <c r="BU5" s="25" t="n"/>
@@ -2690,16 +2724,17 @@
       <c r="CM5" s="24" t="n"/>
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
+      <c r="CP5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>bf114af371174342</t>
+          <t>88cc97b596d74479</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:21.466032Z</t>
+          <t>2026-08-02T13:08:03.938703Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -2753,11 +2788,11 @@
         <v>0.680511</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>0.765271</v>
+        <v>0.765342</v>
       </c>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
-        <v>0.08476</v>
+        <v>0.084831</v>
       </c>
       <c r="R6" s="26" t="n">
         <v>62</v>
@@ -2870,7 +2905,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
+          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2885,7 +2920,7 @@
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>1f55aa19a0c384c21eb0f19669a29e002f639fc5ecd75119e5a949ae308010c1</t>
+          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2905,7 +2940,7 @@
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:16.849872Z</t>
+          <t>2026-08-02T13:07:59.600687Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">
@@ -2951,6 +2986,7 @@
       <c r="CM6" s="24" t="n"/>
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -2729,12 +2729,12 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>88cc97b596d74479</t>
+          <t>571e3a4d6aec4384</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:08:03.938703Z</t>
+          <t>2026-08-02T15:51:56.481863Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -2788,11 +2788,11 @@
         <v>0.680511</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>0.765342</v>
+        <v>0.765185</v>
       </c>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
-        <v>0.084831</v>
+        <v>0.084674</v>
       </c>
       <c r="R6" s="26" t="n">
         <v>62</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
+          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>b98a29b6577e189dd00895de0601ed56ba7ae3a1b60ec17c3cf7e5f5e915c817</t>
+          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:59.600687Z</t>
+          <t>2026-08-02T15:51:51.645392Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">
@@ -2986,7 +2986,11 @@
       <c r="CM6" s="24" t="n"/>
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
-      <c r="CP6" s="24" t="n"/>
+      <c r="CP6" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP6" headerRowCount="1">
-  <autoFilter ref="A1:CP6"/>
-  <tableColumns count="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ6" headerRowCount="1">
+  <autoFilter ref="A1:CQ6"/>
+  <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,7 +396,8 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="trade_candidate"/>
+    <tableColumn id="94" name="market_residual_probability"/>
+    <tableColumn id="95" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1011,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP6"/>
+  <dimension ref="A1:CQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1108,8 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="17" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="17" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1577,6 +1579,11 @@
         </is>
       </c>
       <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>market_residual_probability</t>
+        </is>
+      </c>
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1867,6 +1874,7 @@
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2153,6 +2161,7 @@
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2439,6 +2448,7 @@
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
+      <c r="CQ4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2725,16 +2735,17 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
+      <c r="CQ5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>571e3a4d6aec4384</t>
+          <t>44f7308c09fc47d9</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:56.481863Z</t>
+          <t>2026-08-02T16:15:29.850559Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -2905,7 +2916,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2920,7 +2931,7 @@
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>7396f30c00e8ffbb57bb17db34a5d31518247975a363e02d3a4de7207a6e7d1b</t>
+          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2940,7 +2951,7 @@
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:51.645392Z</t>
+          <t>2026-08-02T16:15:24.994619Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">
@@ -2986,7 +2997,8 @@
       <c r="CM6" s="24" t="n"/>
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
-      <c r="CP6" s="24" t="inlineStr">
+      <c r="CP6" s="24" t="n"/>
+      <c r="CQ6" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -2740,12 +2740,12 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>44f7308c09fc47d9</t>
+          <t>0ace2e7fb1b94cc1</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:29.850559Z</t>
+          <t>2026-08-02T16:53:48.546068Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>b4c26750ab388326010d538858d6e6c8ba3b09468bc7a6123cb5ecb526fbe63f</t>
+          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:24.994619Z</t>
+          <t>2026-08-02T16:53:43.967259Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ6" headerRowCount="1">
-  <autoFilter ref="A1:CQ6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ5" headerRowCount="1">
+  <autoFilter ref="A1:CQ5"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$6)</f>
+        <f>COUNTA('Picks'!$A$2:$A$5)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$6,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$5,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")+COUNTIFS('Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$6,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$5,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")/(COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")+COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")/(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$6)/SUM('Picks'!$BX$2:$BX$6),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$5)/SUM('Picks'!$BX$2:$BX$5),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$6)</f>
+        <f>SUM('Picks'!$BY$2:$BY$5)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$6,"&lt;&gt;",'Picks'!$AB$2:$AB$6),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$5,"&lt;&gt;",'Picks'!$AB$2:$AB$5),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$6,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$6,'Picks'!$AM$2:$AM$6,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$5,'Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ6"/>
+  <dimension ref="A1:CQ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2737,273 +2737,6 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
-        <is>
-          <t>0ace2e7fb1b94cc1</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:48.546068Z</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>67569</t>
-        </is>
-      </c>
-      <c r="E6" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F6" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="G6" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="H6" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I6" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J6" s="25" t="n"/>
-      <c r="K6" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L6" s="26" t="n">
-        <v>-213</v>
-      </c>
-      <c r="M6" s="27" t="n">
-        <v>1.469484</v>
-      </c>
-      <c r="N6" s="28" t="n">
-        <v>0.680511</v>
-      </c>
-      <c r="O6" s="28" t="n">
-        <v>0.765185</v>
-      </c>
-      <c r="P6" s="28" t="n"/>
-      <c r="Q6" s="28" t="n">
-        <v>0.084674</v>
-      </c>
-      <c r="R6" s="26" t="n">
-        <v>62</v>
-      </c>
-      <c r="S6" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U6" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="n"/>
-      <c r="W6" s="26" t="n"/>
-      <c r="X6" s="26" t="n"/>
-      <c r="Y6" s="25" t="n"/>
-      <c r="Z6" s="26" t="n"/>
-      <c r="AA6" s="28" t="n"/>
-      <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="24" t="n"/>
-      <c r="AE6" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF6" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG6" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH6" s="24" t="n"/>
-      <c r="AI6" s="31" t="n"/>
-      <c r="AJ6" s="31" t="n"/>
-      <c r="AK6" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL6" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM6" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN6" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO6" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP6" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AQ6" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AR6" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AS6" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AT6" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AU6" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AV6" s="24" t="n"/>
-      <c r="AW6" s="24" t="n"/>
-      <c r="AX6" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY6" s="24" t="n"/>
-      <c r="AZ6" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA6" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BB6" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC6" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD6" s="24" t="inlineStr">
-        <is>
-          <t>5083ad475aa06c6aaebe6cecb3ef09be7c030e953edab549b4bdaa8c9aa840f9</t>
-        </is>
-      </c>
-      <c r="BE6" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF6" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG6" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH6" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:43.967259Z</t>
-        </is>
-      </c>
-      <c r="BI6" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ6" s="25" t="n"/>
-      <c r="BK6" s="26" t="n">
-        <v>-213</v>
-      </c>
-      <c r="BL6" s="27" t="n">
-        <v>1.469484</v>
-      </c>
-      <c r="BM6" s="28" t="n">
-        <v>0.680511</v>
-      </c>
-      <c r="BN6" s="28" t="n"/>
-      <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
-      <c r="BR6" s="28" t="n"/>
-      <c r="BS6" s="28" t="n"/>
-      <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="25" t="n"/>
-      <c r="BV6" s="29" t="n"/>
-      <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="30" t="n"/>
-      <c r="BY6" s="27" t="n"/>
-      <c r="BZ6" s="24" t="n"/>
-      <c r="CA6" s="31" t="n"/>
-      <c r="CB6" s="24" t="n"/>
-      <c r="CC6" s="24" t="n"/>
-      <c r="CD6" s="24" t="n"/>
-      <c r="CE6" s="24" t="n"/>
-      <c r="CF6" s="24" t="n"/>
-      <c r="CG6" s="24" t="n"/>
-      <c r="CH6" s="24" t="n"/>
-      <c r="CI6" s="24" t="n"/>
-      <c r="CJ6" s="24" t="n"/>
-      <c r="CK6" s="24" t="n"/>
-      <c r="CL6" s="24" t="n"/>
-      <c r="CM6" s="24" t="n"/>
-      <c r="CN6" s="24" t="n"/>
-      <c r="CO6" s="24" t="n"/>
-      <c r="CP6" s="24" t="n"/>
-      <c r="CQ6" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ5" headerRowCount="1">
-  <autoFilter ref="A1:CQ5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ6" headerRowCount="1">
+  <autoFilter ref="A1:CQ6"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$5)</f>
+        <f>COUNTA('Picks'!$A$2:$A$6)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$5,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$6,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")+COUNTIFS('Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$5,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$6,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")/(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")/(COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")+COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$5)/SUM('Picks'!$BX$2:$BX$5),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$6)/SUM('Picks'!$BX$2:$BX$6),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$5)</f>
+        <f>SUM('Picks'!$BY$2:$BY$6)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$5,"&lt;&gt;",'Picks'!$AB$2:$AB$5),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$6,"&lt;&gt;",'Picks'!$AB$2:$AB$6),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$6,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$5,'Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$6,'Picks'!$AM$2:$AM$6,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ5"/>
+  <dimension ref="A1:CQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2737,6 +2737,273 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
     </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>64ab05df273143e5</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:56.490286Z</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O6" s="28" t="n">
+        <v>0.765185</v>
+      </c>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="28" t="n">
+        <v>0.074783</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="S6" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U6" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="n"/>
+      <c r="W6" s="26" t="n"/>
+      <c r="X6" s="26" t="n"/>
+      <c r="Y6" s="25" t="n"/>
+      <c r="Z6" s="26" t="n"/>
+      <c r="AA6" s="28" t="n"/>
+      <c r="AB6" s="28" t="n"/>
+      <c r="AC6" s="30" t="n"/>
+      <c r="AD6" s="24" t="n"/>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG6" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH6" s="24" t="n"/>
+      <c r="AI6" s="31" t="n"/>
+      <c r="AJ6" s="31" t="n"/>
+      <c r="AK6" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN6" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP6" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AQ6" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AR6" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AS6" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AT6" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AU6" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AV6" s="24" t="n"/>
+      <c r="AW6" s="24" t="n"/>
+      <c r="AX6" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY6" s="24" t="n"/>
+      <c r="AZ6" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA6" s="24" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="BB6" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD6" s="24" t="inlineStr">
+        <is>
+          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+        </is>
+      </c>
+      <c r="BE6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:51.807690Z</t>
+        </is>
+      </c>
+      <c r="BI6" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ6" s="25" t="n"/>
+      <c r="BK6" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL6" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM6" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN6" s="28" t="n"/>
+      <c r="BO6" s="28" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
+      <c r="BR6" s="28" t="n"/>
+      <c r="BS6" s="28" t="n"/>
+      <c r="BT6" s="28" t="n"/>
+      <c r="BU6" s="25" t="n"/>
+      <c r="BV6" s="29" t="n"/>
+      <c r="BW6" s="24" t="n"/>
+      <c r="BX6" s="30" t="n"/>
+      <c r="BY6" s="27" t="n"/>
+      <c r="BZ6" s="24" t="n"/>
+      <c r="CA6" s="31" t="n"/>
+      <c r="CB6" s="24" t="n"/>
+      <c r="CC6" s="24" t="n"/>
+      <c r="CD6" s="24" t="n"/>
+      <c r="CE6" s="24" t="n"/>
+      <c r="CF6" s="24" t="n"/>
+      <c r="CG6" s="24" t="n"/>
+      <c r="CH6" s="24" t="n"/>
+      <c r="CI6" s="24" t="n"/>
+      <c r="CJ6" s="24" t="n"/>
+      <c r="CK6" s="24" t="n"/>
+      <c r="CL6" s="24" t="n"/>
+      <c r="CM6" s="24" t="n"/>
+      <c r="CN6" s="24" t="n"/>
+      <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
+      <c r="CQ6" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -2740,12 +2740,12 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>64ab05df273143e5</t>
+          <t>b455449b3f974fd5</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:56.490286Z</t>
+          <t>2026-08-02T18:09:24.902767Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -2799,11 +2799,11 @@
         <v>0.690402</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>0.765185</v>
+        <v>0.765342</v>
       </c>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
-        <v>0.074783</v>
+        <v>0.07494000000000001</v>
       </c>
       <c r="R6" s="26" t="n">
         <v>57</v>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>58e5b3721cf8906aae10d08de8cbb41fd662d66dfb5fe49c8d3ab04bb0741ed6</t>
+          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:51.807690Z</t>
+          <t>2026-08-02T18:09:20.414393Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ6" headerRowCount="1">
-  <autoFilter ref="A1:CQ6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ5" headerRowCount="1">
+  <autoFilter ref="A1:CQ5"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$6)</f>
+        <f>COUNTA('Picks'!$A$2:$A$5)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$6,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$5,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")+COUNTIFS('Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$6,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$5,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")/(COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")+COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")/(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$6)/SUM('Picks'!$BX$2:$BX$6),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$5)/SUM('Picks'!$BX$2:$BX$5),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$6)</f>
+        <f>SUM('Picks'!$BY$2:$BY$5)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$6,"&lt;&gt;",'Picks'!$AB$2:$AB$6),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$5,"&lt;&gt;",'Picks'!$AB$2:$AB$5),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$6,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$6,'Picks'!$AM$2:$AM$6,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$5,'Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ6"/>
+  <dimension ref="A1:CQ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2737,273 +2737,6 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
     </row>
-    <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
-        <is>
-          <t>b455449b3f974fd5</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:24.902767Z</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T15:00:00Z</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
-        <is>
-          <t>67569</t>
-        </is>
-      </c>
-      <c r="E6" s="24" t="inlineStr">
-        <is>
-          <t>VALORANT</t>
-        </is>
-      </c>
-      <c r="F6" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="G6" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="H6" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I6" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J6" s="25" t="n"/>
-      <c r="K6" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L6" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M6" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N6" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O6" s="28" t="n">
-        <v>0.765342</v>
-      </c>
-      <c r="P6" s="28" t="n"/>
-      <c r="Q6" s="28" t="n">
-        <v>0.07494000000000001</v>
-      </c>
-      <c r="R6" s="26" t="n">
-        <v>57</v>
-      </c>
-      <c r="S6" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T6" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U6" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="n"/>
-      <c r="W6" s="26" t="n"/>
-      <c r="X6" s="26" t="n"/>
-      <c r="Y6" s="25" t="n"/>
-      <c r="Z6" s="26" t="n"/>
-      <c r="AA6" s="28" t="n"/>
-      <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="24" t="n"/>
-      <c r="AE6" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF6" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG6" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH6" s="24" t="n"/>
-      <c r="AI6" s="31" t="n"/>
-      <c r="AJ6" s="31" t="n"/>
-      <c r="AK6" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL6" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM6" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN6" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO6" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP6" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AQ6" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AR6" s="24" t="inlineStr">
-        <is>
-          <t>FOKUS Sakura</t>
-        </is>
-      </c>
-      <c r="AS6" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AT6" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AU6" s="24" t="inlineStr">
-        <is>
-          <t>SK Nebula</t>
-        </is>
-      </c>
-      <c r="AV6" s="24" t="n"/>
-      <c r="AW6" s="24" t="n"/>
-      <c r="AX6" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY6" s="24" t="n"/>
-      <c r="AZ6" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA6" s="24" t="inlineStr">
-        <is>
-          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
-        </is>
-      </c>
-      <c r="BB6" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC6" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD6" s="24" t="inlineStr">
-        <is>
-          <t>7b357ebf15fdd8ef9fd17ea55a79657deb8605877a4ca2b29d2bc94bcaa6b578</t>
-        </is>
-      </c>
-      <c r="BE6" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF6" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG6" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH6" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:09:20.414393Z</t>
-        </is>
-      </c>
-      <c r="BI6" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ6" s="25" t="n"/>
-      <c r="BK6" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL6" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM6" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN6" s="28" t="n"/>
-      <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
-      <c r="BR6" s="28" t="n"/>
-      <c r="BS6" s="28" t="n"/>
-      <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="25" t="n"/>
-      <c r="BV6" s="29" t="n"/>
-      <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="30" t="n"/>
-      <c r="BY6" s="27" t="n"/>
-      <c r="BZ6" s="24" t="n"/>
-      <c r="CA6" s="31" t="n"/>
-      <c r="CB6" s="24" t="n"/>
-      <c r="CC6" s="24" t="n"/>
-      <c r="CD6" s="24" t="n"/>
-      <c r="CE6" s="24" t="n"/>
-      <c r="CF6" s="24" t="n"/>
-      <c r="CG6" s="24" t="n"/>
-      <c r="CH6" s="24" t="n"/>
-      <c r="CI6" s="24" t="n"/>
-      <c r="CJ6" s="24" t="n"/>
-      <c r="CK6" s="24" t="n"/>
-      <c r="CL6" s="24" t="n"/>
-      <c r="CM6" s="24" t="n"/>
-      <c r="CN6" s="24" t="n"/>
-      <c r="CO6" s="24" t="n"/>
-      <c r="CP6" s="24" t="n"/>
-      <c r="CQ6" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ5" headerRowCount="1">
-  <autoFilter ref="A1:CQ5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ6" headerRowCount="1">
+  <autoFilter ref="A1:CQ6"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$5)</f>
+        <f>COUNTA('Picks'!$A$2:$A$6)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$5,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$6,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")+COUNTIFS('Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$5,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$6,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")/(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")/(COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")+COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$5)/SUM('Picks'!$BX$2:$BX$5),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$6)/SUM('Picks'!$BX$2:$BX$6),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$5)</f>
+        <f>SUM('Picks'!$BY$2:$BY$6)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$5,"&lt;&gt;",'Picks'!$AB$2:$AB$5),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$6,"&lt;&gt;",'Picks'!$AB$2:$AB$6),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$6,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$5,'Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$6,'Picks'!$AM$2:$AM$6,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ5"/>
+  <dimension ref="A1:CQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2737,6 +2737,273 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
     </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>9f9208263c4547c2</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:13.369760Z</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>67569</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O6" s="28" t="n">
+        <v>0.765342</v>
+      </c>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="28" t="n">
+        <v>0.07494000000000001</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="S6" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U6" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="n"/>
+      <c r="W6" s="26" t="n"/>
+      <c r="X6" s="26" t="n"/>
+      <c r="Y6" s="25" t="n"/>
+      <c r="Z6" s="26" t="n"/>
+      <c r="AA6" s="28" t="n"/>
+      <c r="AB6" s="28" t="n"/>
+      <c r="AC6" s="30" t="n"/>
+      <c r="AD6" s="24" t="n"/>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG6" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH6" s="24" t="n"/>
+      <c r="AI6" s="31" t="n"/>
+      <c r="AJ6" s="31" t="n"/>
+      <c r="AK6" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN6" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO6" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP6" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AQ6" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AR6" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AS6" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AT6" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AU6" s="24" t="inlineStr">
+        <is>
+          <t>SK Nebula</t>
+        </is>
+      </c>
+      <c r="AV6" s="24" t="n"/>
+      <c r="AW6" s="24" t="n"/>
+      <c r="AX6" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY6" s="24" t="n"/>
+      <c r="AZ6" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA6" s="24" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="BB6" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD6" s="24" t="inlineStr">
+        <is>
+          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+        </is>
+      </c>
+      <c r="BE6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG6" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:08.752039Z</t>
+        </is>
+      </c>
+      <c r="BI6" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ6" s="25" t="n"/>
+      <c r="BK6" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL6" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM6" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN6" s="28" t="n"/>
+      <c r="BO6" s="28" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
+      <c r="BR6" s="28" t="n"/>
+      <c r="BS6" s="28" t="n"/>
+      <c r="BT6" s="28" t="n"/>
+      <c r="BU6" s="25" t="n"/>
+      <c r="BV6" s="29" t="n"/>
+      <c r="BW6" s="24" t="n"/>
+      <c r="BX6" s="30" t="n"/>
+      <c r="BY6" s="27" t="n"/>
+      <c r="BZ6" s="24" t="n"/>
+      <c r="CA6" s="31" t="n"/>
+      <c r="CB6" s="24" t="n"/>
+      <c r="CC6" s="24" t="n"/>
+      <c r="CD6" s="24" t="n"/>
+      <c r="CE6" s="24" t="n"/>
+      <c r="CF6" s="24" t="n"/>
+      <c r="CG6" s="24" t="n"/>
+      <c r="CH6" s="24" t="n"/>
+      <c r="CI6" s="24" t="n"/>
+      <c r="CJ6" s="24" t="n"/>
+      <c r="CK6" s="24" t="n"/>
+      <c r="CL6" s="24" t="n"/>
+      <c r="CM6" s="24" t="n"/>
+      <c r="CN6" s="24" t="n"/>
+      <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
+      <c r="CQ6" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -2740,12 +2740,12 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>9f9208263c4547c2</t>
+          <t>ad8fa896c5344f29</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:13.369760Z</t>
+          <t>2026-08-03T13:30:41.417037Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -2790,23 +2790,23 @@
         </is>
       </c>
       <c r="L6" s="26" t="n">
-        <v>-223</v>
+        <v>-163</v>
       </c>
       <c r="M6" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.613497</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.619772</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>0.765342</v>
+        <v>0.765423</v>
       </c>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
-        <v>0.07494000000000001</v>
+        <v>0.145651</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="S6" s="29" t="n">
         <v>2</v>
@@ -2818,21 +2818,41 @@
       </c>
       <c r="U6" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="n"/>
-      <c r="W6" s="26" t="n"/>
-      <c r="X6" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y6" s="25" t="n"/>
-      <c r="Z6" s="26" t="n"/>
-      <c r="AA6" s="28" t="n"/>
-      <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="24" t="n"/>
+      <c r="Z6" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="AA6" s="28" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AB6" s="28" t="n">
+        <v>0.000228</v>
+      </c>
+      <c r="AC6" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:06:06.463819Z</t>
+        </is>
+      </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
         </is>
       </c>
       <c r="AF6" s="31" t="inlineStr">
@@ -2842,7 +2862,7 @@
       </c>
       <c r="AG6" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH6" s="24" t="n"/>
@@ -2916,7 +2936,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+          <t>afe2fffd3c666e0d8f9040dcc6dedae587629fd14dee7043c87557d9d9d9e6e5</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2931,7 +2951,7 @@
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>aa63798f2910846053904184b00fe7ab3d234b671e36f3972069106b36a79e32</t>
+          <t>afe2fffd3c666e0d8f9040dcc6dedae587629fd14dee7043c87557d9d9d9e6e5</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2951,7 +2971,7 @@
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:25:08.752039Z</t>
+          <t>2026-08-03T13:30:33.637118Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">
@@ -2961,19 +2981,23 @@
       </c>
       <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
-        <v>-223</v>
+        <v>-163</v>
       </c>
       <c r="BL6" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.613497</v>
       </c>
       <c r="BM6" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.619772</v>
       </c>
       <c r="BN6" s="28" t="n"/>
       <c r="BO6" s="28" t="n"/>
       <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
-      <c r="BR6" s="28" t="n"/>
+      <c r="BQ6" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BR6" s="28" t="n">
+        <v>0.62</v>
+      </c>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
       <c r="BU6" s="25" t="n"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ6" headerRowCount="1">
-  <autoFilter ref="A1:CQ6"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR7" headerRowCount="1">
+  <autoFilter ref="A1:CR7"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$6)</f>
+        <f>COUNTA('Picks'!$A$2:$A$7)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$6,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$7,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")+COUNTIFS('Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$6,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$7,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")/(COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"win")+COUNTIFS('Picks'!$BX$2:$BX$6,"&gt;0",'Picks'!$V$2:$V$6,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")/(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$6)/SUM('Picks'!$BX$2:$BX$6),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$7)/SUM('Picks'!$BX$2:$BX$7),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$6)</f>
+        <f>SUM('Picks'!$BY$2:$BY$7)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$6,"&lt;&gt;",'Picks'!$AB$2:$AB$6),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$7,"&lt;&gt;",'Picks'!$AB$2:$AB$7),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$6,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$6,'Picks'!$AM$2:$AM$6,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$7,'Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A14,'Picks'!$U$2:$U$6,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A15,'Picks'!$U$2:$U$6,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled",'Picks'!$V$2:$V$6,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$6,'Picks'!$H$2:$H$6,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$6,'Picks'!$H$2:$H$6,$A16,'Picks'!$U$2:$U$6,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ6"/>
+  <dimension ref="A1:CR7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1875,6 +1882,7 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2162,6 +2170,7 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2449,6 +2458,7 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2736,6 +2746,7 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3022,7 +3033,276 @@
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
-      <c r="CQ6" s="24" t="inlineStr">
+      <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>a79d92e3130d41b5</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:26.878542Z</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N7" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O7" s="28" t="n">
+        <v>0.568122</v>
+      </c>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="28" t="n">
+        <v>0.098638</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="S7" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="n"/>
+      <c r="W7" s="26" t="n"/>
+      <c r="X7" s="26" t="n"/>
+      <c r="Y7" s="25" t="n"/>
+      <c r="Z7" s="26" t="n"/>
+      <c r="AA7" s="28" t="n"/>
+      <c r="AB7" s="28" t="n"/>
+      <c r="AC7" s="30" t="n"/>
+      <c r="AD7" s="24" t="n"/>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG7" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH7" s="24" t="n"/>
+      <c r="AI7" s="31" t="n"/>
+      <c r="AJ7" s="31" t="n"/>
+      <c r="AK7" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN7" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO7" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP7" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AQ7" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AR7" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AS7" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="AT7" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="AU7" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="AV7" s="24" t="n"/>
+      <c r="AW7" s="24" t="n"/>
+      <c r="AX7" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY7" s="24" t="n"/>
+      <c r="AZ7" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA7" s="24" t="inlineStr">
+        <is>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+        </is>
+      </c>
+      <c r="BB7" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC7" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD7" s="24" t="inlineStr">
+        <is>
+          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+        </is>
+      </c>
+      <c r="BE7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG7" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:24.642540Z</t>
+        </is>
+      </c>
+      <c r="BI7" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ7" s="25" t="n"/>
+      <c r="BK7" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL7" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM7" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN7" s="28" t="n"/>
+      <c r="BO7" s="28" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
+      <c r="BR7" s="28" t="n"/>
+      <c r="BS7" s="28" t="n"/>
+      <c r="BT7" s="28" t="n"/>
+      <c r="BU7" s="25" t="n"/>
+      <c r="BV7" s="29" t="n"/>
+      <c r="BW7" s="24" t="n"/>
+      <c r="BX7" s="30" t="n"/>
+      <c r="BY7" s="27" t="n"/>
+      <c r="BZ7" s="24" t="n"/>
+      <c r="CA7" s="31" t="n"/>
+      <c r="CB7" s="24" t="n"/>
+      <c r="CC7" s="24" t="n"/>
+      <c r="CD7" s="24" t="n"/>
+      <c r="CE7" s="24" t="n"/>
+      <c r="CF7" s="24" t="n"/>
+      <c r="CG7" s="24" t="n"/>
+      <c r="CH7" s="24" t="n"/>
+      <c r="CI7" s="24" t="n"/>
+      <c r="CJ7" s="24" t="n"/>
+      <c r="CK7" s="24" t="n"/>
+      <c r="CL7" s="24" t="n"/>
+      <c r="CM7" s="24" t="n"/>
+      <c r="CN7" s="24" t="n"/>
+      <c r="CO7" s="24" t="n"/>
+      <c r="CP7" s="24" t="n"/>
+      <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR7" headerRowCount="1">
-  <autoFilter ref="A1:CR7"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS7" headerRowCount="1">
+  <autoFilter ref="A1:CS7"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR7"/>
+  <dimension ref="A1:CS7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1883,6 +1890,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2171,6 +2179,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2459,6 +2468,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2747,6 +2757,7 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3034,7 +3045,8 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
-      <c r="CR6" s="24" t="inlineStr">
+      <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3043,12 +3055,12 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>a79d92e3130d41b5</t>
+          <t>b1961ac6c1214eca</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:26.878542Z</t>
+          <t>2026-08-04T14:26:45.561526Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
@@ -3093,23 +3105,23 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.460829</v>
       </c>
       <c r="O7" s="28" t="n">
         <v>0.568122</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.098638</v>
+        <v>0.107293</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="S7" s="29" t="n">
         <v>1</v>
@@ -3135,7 +3147,7 @@
       <c r="AD7" s="24" t="n"/>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3219,7 +3231,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3234,7 +3246,7 @@
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>c9682bbbcb8946e5c92bb584af88ebbd8fda9c7d2724928c51c2d918ea8bca24</t>
+          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3254,7 +3266,7 @@
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:24.642540Z</t>
+          <t>2026-08-04T14:26:42.943962Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3264,13 +3276,13 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.460829</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
@@ -3302,7 +3314,8 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
-      <c r="CR7" s="24" t="inlineStr">
+      <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS7" headerRowCount="1">
-  <autoFilter ref="A1:CS7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS12" headerRowCount="1">
+  <autoFilter ref="A1:CS12"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$7)</f>
+        <f>COUNTA('Picks'!$A$2:$A$12)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$7,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$12,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$7,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$12,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")/(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")/(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$7)/SUM('Picks'!$BX$2:$BX$7),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$12)/SUM('Picks'!$BX$2:$BX$12),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$7)</f>
+        <f>SUM('Picks'!$BY$2:$BY$12)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$7,"&lt;&gt;",'Picks'!$AB$2:$AB$7),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$12,"&lt;&gt;",'Picks'!$AB$2:$AB$12),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$7,'Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$12,'Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS7"/>
+  <dimension ref="A1:CS12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3055,22 +3055,22 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>b1961ac6c1214eca</t>
+          <t>993252575c7e4976</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:45.561526Z</t>
+          <t>2026-08-04T16:54:18.134287Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T10:00:00Z</t>
+          <t>2026-08-04T18:00:00Z</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>69540</t>
+          <t>68698</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>KeepBest Gaming</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>TEC Esports</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="I7" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J7" s="25" t="n"/>
@@ -3105,49 +3105,69 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>117</v>
+        <v>-163</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>2.17</v>
+        <v>1.613497</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.619772</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.568122</v>
+        <v>0.64657</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.107293</v>
+        <v>0.026798</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="S7" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T7" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U7" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+      <c r="X7" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
-      <c r="Z7" s="26" t="n"/>
-      <c r="AA7" s="28" t="n"/>
-      <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="Z7" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA7" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB7" s="28" t="n">
+        <v>0.010228</v>
+      </c>
+      <c r="AC7" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:12.102961Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-skn-tmo-2026-08-04).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3157,7 +3177,7 @@
       </c>
       <c r="AG7" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH7" s="24" t="n"/>
@@ -3188,32 +3208,32 @@
       </c>
       <c r="AP7" s="24" t="inlineStr">
         <is>
-          <t>KeepBest Gaming</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AQ7" s="24" t="inlineStr">
         <is>
-          <t>KeepBest Gaming</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AR7" s="24" t="inlineStr">
         <is>
-          <t>KeepBest Gaming</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AS7" s="24" t="inlineStr">
         <is>
-          <t>TEC Esports</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AT7" s="24" t="inlineStr">
         <is>
-          <t>TEC Esports</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AU7" s="24" t="inlineStr">
         <is>
-          <t>TEC Esports</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AV7" s="24" t="n"/>
@@ -3231,7 +3251,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
+          <t>2a3a3c0d919df15db76d78df508a996bd8f684ec881c5b644b1e53da56868427</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3241,12 +3261,12 @@
       </c>
       <c r="BC7" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
+          <t>2a3a3c0d919df15db76d78df508a996bd8f684ec881c5b644b1e53da56868427</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3261,12 +3281,12 @@
       </c>
       <c r="BG7" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:42.943962Z</t>
+          <t>2026-08-04T16:54:14.515679Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3276,19 +3296,23 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>117</v>
+        <v>-163</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>2.17</v>
+        <v>1.613497</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.619772</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
       <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
-      <c r="BR7" s="28" t="n"/>
+      <c r="BQ7" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR7" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
       <c r="BU7" s="25" t="n"/>
@@ -3321,6 +3345,1351 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>fbbd225f128542cc</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.842798Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.575198</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>0.124748</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="n"/>
+      <c r="W8" s="26" t="n"/>
+      <c r="X8" s="26" t="n"/>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n"/>
+      <c r="AD8" s="24" t="n"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:10.028876Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN8" s="28" t="n"/>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+      <c r="CB8" s="24" t="n"/>
+      <c r="CC8" s="24" t="n"/>
+      <c r="CD8" s="24" t="n"/>
+      <c r="CE8" s="24" t="n"/>
+      <c r="CF8" s="24" t="n"/>
+      <c r="CG8" s="24" t="n"/>
+      <c r="CH8" s="24" t="n"/>
+      <c r="CI8" s="24" t="n"/>
+      <c r="CJ8" s="24" t="n"/>
+      <c r="CK8" s="24" t="n"/>
+      <c r="CL8" s="24" t="n"/>
+      <c r="CM8" s="24" t="n"/>
+      <c r="CN8" s="24" t="n"/>
+      <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
+      <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>ebcabc7cdc864bd9</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.842798Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>70564</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>FunPlus Phoenix</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.669245</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.05987</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-valorant-fpx-jdg-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>JD Gaming</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>FunPlus Phoenix</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>FunPlus Phoenix</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>FunPlus Phoenix</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:14.218178Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>e93e40b1f3124d0d</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.842798Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.702781</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>0.312156</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="n"/>
+      <c r="W10" s="26" t="n"/>
+      <c r="X10" s="26" t="n"/>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n"/>
+      <c r="AD10" s="24" t="n"/>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-gx-sge-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:15.903165Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>4f79900dc9744cdd</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.842798Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.564051</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.193681</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-valorant-navi-jl-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:18.444919Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>377c33437bf243e9</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.842798Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.626622</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>0.176172</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="26" t="n"/>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n"/>
+      <c r="AD12" s="24" t="n"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-valorant-eg-fur-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.044205Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -3426,18 +3426,38 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
-      <c r="Z8" s="26" t="n"/>
-      <c r="AA8" s="28" t="n"/>
-      <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="Z8" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA8" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB8" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC8" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:01.477710Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
@@ -3450,7 +3470,7 @@
       </c>
       <c r="AG8" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH8" s="24" t="n"/>
@@ -3580,8 +3600,12 @@
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
       <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
-      <c r="BR8" s="28" t="n"/>
+      <c r="BQ8" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR8" s="28" t="n">
+        <v>0.45</v>
+      </c>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
       <c r="BU8" s="25" t="n"/>
@@ -3617,12 +3641,12 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>ebcabc7cdc864bd9</t>
+          <t>8abc0e8aacc448df</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.842798Z</t>
+          <t>2026-08-05T13:56:15.301935Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
@@ -3676,14 +3700,14 @@
         <v>0.609375</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.669245</v>
+        <v>0.667906</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.05987</v>
+        <v>0.058531</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S9" s="29" t="n">
         <v>1.75</v>
@@ -3793,7 +3817,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3808,7 +3832,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3828,7 +3852,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:14.218178Z</t>
+          <t>2026-08-05T13:56:10.639279Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3886,12 +3910,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>e93e40b1f3124d0d</t>
+          <t>b00204812ce843a3</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.842798Z</t>
+          <t>2026-08-05T13:56:15.301935Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -3945,11 +3969,11 @@
         <v>0.390625</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.702781</v>
+        <v>0.701767</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>0.312156</v>
+        <v>0.311142</v>
       </c>
       <c r="R10" s="26" t="n">
         <v>100</v>
@@ -4062,7 +4086,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4077,7 +4101,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4097,7 +4121,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:15.903165Z</t>
+          <t>2026-08-05T13:56:11.760518Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4155,12 +4179,12 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>4f79900dc9744cdd</t>
+          <t>8eebbb99244b474f</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.842798Z</t>
+          <t>2026-08-05T13:56:15.301935Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
@@ -4214,11 +4238,11 @@
         <v>0.37037</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.564051</v>
+        <v>0.563896</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.193681</v>
+        <v>0.193526</v>
       </c>
       <c r="R11" s="26" t="n">
         <v>100</v>
@@ -4331,7 +4355,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4346,7 +4370,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4366,7 +4390,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:18.444919Z</t>
+          <t>2026-08-05T13:56:13.229270Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4424,12 +4448,12 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>377c33437bf243e9</t>
+          <t>d11a20f557b747c5</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.842798Z</t>
+          <t>2026-08-05T13:56:15.301935Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
@@ -4474,20 +4498,20 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.420168</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.626622</v>
+        <v>0.625458</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.176172</v>
+        <v>0.20529</v>
       </c>
       <c r="R12" s="26" t="n">
         <v>100</v>
@@ -4516,7 +4540,7 @@
       <c r="AD12" s="24" t="n"/>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-valorant-eg-fur-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-eg-fur-2026-08-06).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4600,7 +4624,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4615,7 +4639,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4635,7 +4659,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.044205Z</t>
+          <t>2026-08-05T13:56:14.786413Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4645,13 +4669,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.420168</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS12" headerRowCount="1">
-  <autoFilter ref="A1:CS12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS14" headerRowCount="1">
+  <autoFilter ref="A1:CS14"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$12)</f>
+        <f>COUNTA('Picks'!$A$2:$A$14)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$12,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")/(COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"win")+COUNTIFS('Picks'!$BX$2:$BX$12,"&gt;0",'Picks'!$V$2:$V$12,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$12)/SUM('Picks'!$BX$2:$BX$12),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$12)</f>
+        <f>SUM('Picks'!$BY$2:$BY$14)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$12,"&lt;&gt;",'Picks'!$AB$2:$AB$12),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$12,'Picks'!$AM$2:$AM$12,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A14,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A15,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled",'Picks'!$V$2:$V$12,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$12,'Picks'!$H$2:$H$12,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$12,'Picks'!$H$2:$H$12,$A16,'Picks'!$U$2:$U$12,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS12"/>
+  <dimension ref="A1:CS14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3641,22 +3641,22 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>8abc0e8aacc448df</t>
+          <t>4afe1804253940e0</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:15.301935Z</t>
+          <t>2026-08-06T00:24:39.463638Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T08:00:00Z</t>
+          <t>2026-08-06T15:00:00Z</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>70564</t>
+          <t>70724</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>JD Gaming</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>FunPlus Phoenix</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J9" s="25" t="n"/>
@@ -3691,26 +3691,26 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>-156</v>
+        <v>138</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>1.641026</v>
+        <v>2.38</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.420168</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.667906</v>
+        <v>0.695761</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.058531</v>
+        <v>0.275593</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="S9" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T9" s="24" t="inlineStr">
         <is>
@@ -3719,21 +3719,35 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:16.552761Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-valorant-fpx-jdg-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-gx-sge-2026-08-06).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3743,7 +3757,7 @@
       </c>
       <c r="AG9" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH9" s="24" t="n"/>
@@ -3774,32 +3788,32 @@
       </c>
       <c r="AP9" s="24" t="inlineStr">
         <is>
-          <t>JD Gaming</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AQ9" s="24" t="inlineStr">
         <is>
-          <t>JD Gaming</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AR9" s="24" t="inlineStr">
         <is>
-          <t>JD Gaming</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AS9" s="24" t="inlineStr">
         <is>
-          <t>FunPlus Phoenix</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="AT9" s="24" t="inlineStr">
         <is>
-          <t>FunPlus Phoenix</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="AU9" s="24" t="inlineStr">
         <is>
-          <t>FunPlus Phoenix</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="AV9" s="24" t="n"/>
@@ -3817,7 +3831,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3832,7 +3846,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3852,7 +3866,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:10.639279Z</t>
+          <t>2026-08-06T00:24:37.569959Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3862,13 +3876,13 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>-156</v>
+        <v>138</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>1.641026</v>
+        <v>2.38</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.420168</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
@@ -3910,22 +3924,22 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>b00204812ce843a3</t>
+          <t>9ac66283b1f0467b</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:15.301935Z</t>
+          <t>2026-08-06T00:24:39.463638Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T15:00:00Z</t>
+          <t>2026-08-06T18:00:00Z</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>70724</t>
+          <t>70912</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3935,12 +3949,12 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -3960,26 +3974,26 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.359712</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.701767</v>
+        <v>0.563029</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>0.311142</v>
+        <v>0.203317</v>
       </c>
       <c r="R10" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S10" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" s="24" t="inlineStr">
         <is>
@@ -3988,21 +4002,35 @@
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:01:54.163030Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-gx-sge-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-valorant-navi-jl-2026-08-06).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -4043,32 +4071,32 @@
       </c>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AQ10" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AR10" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AS10" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AT10" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AU10" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AV10" s="24" t="n"/>
@@ -4086,7 +4114,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4101,7 +4129,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4121,7 +4149,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:11.760518Z</t>
+          <t>2026-08-06T00:24:38.040365Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4131,13 +4159,13 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.359712</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
@@ -4179,22 +4207,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>8eebbb99244b474f</t>
+          <t>33fe14e66f0c4a77</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:15.301935Z</t>
+          <t>2026-08-06T19:00:18.001858Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T18:00:00Z</t>
+          <t>2026-08-06T21:00:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>70912</t>
+          <t>71315</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4204,12 +4232,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>FURIA Esports</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4219,7 +4247,7 @@
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J11" s="25" t="n"/>
@@ -4229,49 +4257,69 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.460829</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.563896</v>
+        <v>0.615411</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.193526</v>
+        <v>0.154582</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="S11" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T11" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U11" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
       <c r="Y11" s="25" t="n"/>
-      <c r="Z11" s="26" t="n"/>
-      <c r="AA11" s="28" t="n"/>
-      <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
+      <c r="Z11" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="AA11" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB11" s="28" t="n">
+        <v>-0.000829</v>
+      </c>
+      <c r="AC11" s="30" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:01:55.454308Z</t>
+        </is>
+      </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-valorant-navi-jl-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-eg-fur-2026-08-06).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4312,32 +4360,32 @@
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>FURIA Esports</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>FURIA Esports</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>FURIA Esports</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4355,7 +4403,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4370,7 +4418,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4390,7 +4438,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:13.229270Z</t>
+          <t>2026-08-06T19:00:13.149018Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4400,19 +4448,23 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.37037</v>
+        <v>0.460829</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
       <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
-      <c r="BR11" s="28" t="n"/>
+      <c r="BQ11" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BR11" s="28" t="n">
+        <v>0.46</v>
+      </c>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
       <c r="BU11" s="25" t="n"/>
@@ -4448,22 +4500,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>d11a20f557b747c5</t>
+          <t>ccd5f17eb0c54739</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:15.301935Z</t>
+          <t>2026-08-07T09:11:28.912966Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T21:00:00Z</t>
+          <t>2026-08-07T11:00:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>71315</t>
+          <t>71752</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4473,12 +4525,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>FURIA Esports</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4498,26 +4550,26 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>138</v>
+        <v>-156</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>2.38</v>
+        <v>1.641026</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.609375</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.625458</v>
+        <v>0.781485</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.20529</v>
+        <v>0.17211</v>
       </c>
       <c r="R12" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
@@ -4526,21 +4578,41 @@
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y12" s="25" t="n"/>
-      <c r="Z12" s="26" t="n"/>
-      <c r="AA12" s="28" t="n"/>
-      <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
+      <c r="Z12" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AA12" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB12" s="28" t="n">
+        <v>0.000625</v>
+      </c>
+      <c r="AC12" s="30" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:06.633818Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-eg-fur-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-valorant-geng-fs-2026-08-07).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4581,32 +4653,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>FURIA Esports</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>FURIA Esports</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>FURIA Esports</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4624,7 +4696,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4639,7 +4711,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>305eb2436fa64b7f6f74f3369a4347588970440da884df1804895fe56c0c5fdd</t>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4659,7 +4731,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:56:14.786413Z</t>
+          <t>2026-08-07T09:11:21.351080Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4669,19 +4741,23 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>138</v>
+        <v>-156</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>2.38</v>
+        <v>1.641026</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.609375</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
       <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
-      <c r="BR12" s="28" t="n"/>
+      <c r="BQ12" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BR12" s="28" t="n">
+        <v>0.61</v>
+      </c>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
       <c r="BU12" s="25" t="n"/>
@@ -4714,6 +4790,544 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>94a64e146f5740da</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:00.757019Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>72078</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.743264</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.383552</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-valorant-fnc-ep-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:54.113763Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>bd6d7471dff44684</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:00.757019Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>74165</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.699272</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>0.319044</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="n"/>
+      <c r="W14" s="26" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-valorant-ef-jl-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:59.578708Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS14" headerRowCount="1">
-  <autoFilter ref="A1:CS14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS15" headerRowCount="1">
+  <autoFilter ref="A1:CS15"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$14)</f>
+        <f>COUNTA('Picks'!$A$2:$A$15)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$14,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$14,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")/(COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"win")+COUNTIFS('Picks'!$BX$2:$BX$14,"&gt;0",'Picks'!$V$2:$V$14,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$14)/SUM('Picks'!$BX$2:$BX$14),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$14)</f>
+        <f>SUM('Picks'!$BY$2:$BY$15)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$14,"&lt;&gt;",'Picks'!$AB$2:$AB$14),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$14,'Picks'!$AM$2:$AM$14,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A14,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A15,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled",'Picks'!$V$2:$V$14,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$14,'Picks'!$H$2:$H$14,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$14,'Picks'!$H$2:$H$14,$A16,'Picks'!$U$2:$U$14,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS14"/>
+  <dimension ref="A1:CS15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5062,22 +5062,22 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>bd6d7471dff44684</t>
+          <t>006c3a9563cc487d</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:00.757019Z</t>
+          <t>2026-08-07T18:31:15.157040Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-08T18:00:00Z</t>
+          <t>2026-08-08T17:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>74165</t>
+          <t>74125</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Lost Puppies GC</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire</t>
+          <t>ALTERNATE aTTaX Ruby</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -5112,26 +5112,26 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>163</v>
+        <v>-113</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>2.63</v>
+        <v>1.884956</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.530516</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.699272</v>
+        <v>0.637346</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.319044</v>
+        <v>0.10683</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
       <c r="AD14" s="24" t="n"/>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-valorant-ef-jl-2026-08-08).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-valorant-aar-lpg-2026-08-08).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5195,32 +5195,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Lost Puppies GC</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Lost Puppies GC</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Lost Puppies GC</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire</t>
+          <t>ALTERNATE aTTaX Ruby</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire</t>
+          <t>ALTERNATE aTTaX Ruby</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire</t>
+          <t>ALTERNATE aTTaX Ruby</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:59.578708Z</t>
+          <t>2026-08-07T18:31:13.105417Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5283,13 +5283,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>163</v>
+        <v>-113</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>2.63</v>
+        <v>1.884956</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.530516</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5328,6 +5328,275 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>a5ab521423d6477e</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:15.157040Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>74165</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.698711</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.318483</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-valorant-ef-jl-2026-08-08).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Eternal Fire</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>ef0c14d41616194039e3a45d03be057b88a2b623729b48186885c27089c38788</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:31:13.626555Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS7" headerRowCount="1">
-  <autoFilter ref="A1:CS7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS25" headerRowCount="1">
+  <autoFilter ref="A1:CS25"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$7)</f>
+        <f>COUNTA('Picks'!$A$2:$A$25)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$7,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$25,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$7,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$25,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")/(COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"win")+COUNTIFS('Picks'!$BX$2:$BX$7,"&gt;0",'Picks'!$V$2:$V$7,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")/(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$7)/SUM('Picks'!$BX$2:$BX$7),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$25)/SUM('Picks'!$BX$2:$BX$25),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$7)</f>
+        <f>SUM('Picks'!$BY$2:$BY$25)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$7,"&lt;&gt;",'Picks'!$AB$2:$AB$7),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$25,"&lt;&gt;",'Picks'!$AB$2:$AB$25),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$7,'Picks'!$AM$2:$AM$7,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$25,'Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A14,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A15,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled",'Picks'!$V$2:$V$7,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$7,'Picks'!$H$2:$H$7,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$7,'Picks'!$H$2:$H$7,$A16,'Picks'!$U$2:$U$7,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS7"/>
+  <dimension ref="A1:CS25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3055,22 +3055,22 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>b1961ac6c1214eca</t>
+          <t>993252575c7e4976</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:45.561526Z</t>
+          <t>2026-08-04T16:54:18.134287Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T10:00:00Z</t>
+          <t>2026-08-04T18:00:00Z</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>69540</t>
+          <t>68698</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>KeepBest Gaming</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>TEC Esports</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="I7" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J7" s="25" t="n"/>
@@ -3105,49 +3105,69 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>117</v>
+        <v>-163</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>2.17</v>
+        <v>1.613497</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.619772</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.568122</v>
+        <v>0.64657</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.107293</v>
+        <v>0.026798</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="S7" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T7" s="24" t="inlineStr">
-        <is>
-          <t>valorant-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U7" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+      <c r="X7" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
-      <c r="Z7" s="26" t="n"/>
-      <c r="AA7" s="28" t="n"/>
-      <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="Z7" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA7" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB7" s="28" t="n">
+        <v>0.010228</v>
+      </c>
+      <c r="AC7" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T22:00:12.102961Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-skn-tmo-2026-08-04).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3157,7 +3177,7 @@
       </c>
       <c r="AG7" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH7" s="24" t="n"/>
@@ -3188,32 +3208,32 @@
       </c>
       <c r="AP7" s="24" t="inlineStr">
         <is>
-          <t>KeepBest Gaming</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AQ7" s="24" t="inlineStr">
         <is>
-          <t>KeepBest Gaming</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AR7" s="24" t="inlineStr">
         <is>
-          <t>KeepBest Gaming</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AS7" s="24" t="inlineStr">
         <is>
-          <t>TEC Esports</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AT7" s="24" t="inlineStr">
         <is>
-          <t>TEC Esports</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AU7" s="24" t="inlineStr">
         <is>
-          <t>TEC Esports</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AV7" s="24" t="n"/>
@@ -3231,7 +3251,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
+          <t>2a3a3c0d919df15db76d78df508a996bd8f684ec881c5b644b1e53da56868427</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3241,12 +3261,12 @@
       </c>
       <c r="BC7" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>c8143bea9617c85b46e357e7a1261b7a10902182c05435f79ef9726aa3473977</t>
+          <t>2a3a3c0d919df15db76d78df508a996bd8f684ec881c5b644b1e53da56868427</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3261,12 +3281,12 @@
       </c>
       <c r="BG7" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T14:26:42.943962Z</t>
+          <t>2026-08-04T16:54:14.515679Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3276,19 +3296,23 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>117</v>
+        <v>-163</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>2.17</v>
+        <v>1.613497</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.619772</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
       <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
-      <c r="BR7" s="28" t="n"/>
+      <c r="BQ7" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR7" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
       <c r="BU7" s="25" t="n"/>
@@ -3321,6 +3345,5058 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>fbbd225f128542cc</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:20.842798Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>69540</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.575198</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>0.124748</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA8" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB8" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC8" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T13:52:01.477710Z</t>
+        </is>
+      </c>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>KeepBest Gaming</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>TEC Esports</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:38:10.028876Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN8" s="28" t="n"/>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR8" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+      <c r="CB8" s="24" t="n"/>
+      <c r="CC8" s="24" t="n"/>
+      <c r="CD8" s="24" t="n"/>
+      <c r="CE8" s="24" t="n"/>
+      <c r="CF8" s="24" t="n"/>
+      <c r="CG8" s="24" t="n"/>
+      <c r="CH8" s="24" t="n"/>
+      <c r="CI8" s="24" t="n"/>
+      <c r="CJ8" s="24" t="n"/>
+      <c r="CK8" s="24" t="n"/>
+      <c r="CL8" s="24" t="n"/>
+      <c r="CM8" s="24" t="n"/>
+      <c r="CN8" s="24" t="n"/>
+      <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
+      <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>4afe1804253940e0</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:39.463638Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>70724</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.695761</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>0.275593</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:57:16.552761Z</t>
+        </is>
+      </c>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-gx-sge-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>GIANTX</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:37.569959Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>9ac66283b1f0467b</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:39.463638Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>70912</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.563029</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>0.203317</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:01:54.163030Z</t>
+        </is>
+      </c>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-valorant-navi-jl-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>Joblife</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:24:38.040365Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>33fe14e66f0c4a77</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:18.001858Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>71315</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.615411</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>0.154582</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>97</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="AA11" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB11" s="28" t="n">
+        <v>-0.000829</v>
+      </c>
+      <c r="AC11" s="30" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:01:55.454308Z</t>
+        </is>
+      </c>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-eg-fur-2026-08-06).</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Evil Geniuses</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-06T19:00:13.149018Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BR11" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>ccd5f17eb0c54739</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:28.912966Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>71752</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>FULL SENSE</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.781485</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>0.17211</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AA12" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB12" s="28" t="n">
+        <v>0.000625</v>
+      </c>
+      <c r="AC12" s="30" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:20:06.633818Z</t>
+        </is>
+      </c>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-valorant-geng-fs-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>FULL SENSE</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>FULL SENSE</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>FULL SENSE</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>Gen.G Esports</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:11:21.351080Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BR12" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>94a64e146f5740da</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:24:00.757019Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>72078</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.743264</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>0.383552</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="AA13" s="28" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB13" s="28" t="n">
+        <v>0.000288</v>
+      </c>
+      <c r="AC13" s="30" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T21:55:39.052370Z</t>
+        </is>
+      </c>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-valorant-fnc-ep-2026-08-07).</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T15:23:54.113763Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.359712</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BR13" s="28" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>e501297caddc4e51</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:08:20.055519Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>74609</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.804725</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>0.404725</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA14" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB14" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:26:25.086079Z</t>
+        </is>
+      </c>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-valorant-gm-ep-2026-08-09).</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Enterprise Esports</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>43316dd49e7f9b1a20757c6d2b94b720f27a77b2c5fd90af5fff6a8c8dacabc4</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>43316dd49e7f9b1a20757c6d2b94b720f27a77b2c5fd90af5fff6a8c8dacabc4</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:08:10.558137Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR14" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>7ab28900c23e400a</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:36:45.039622Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>75255</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Olimpo Gold</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>NPC Team</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.559409</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>0.159409</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA15" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB15" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T13:09:08.912134Z</t>
+        </is>
+      </c>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-valorant-ntp-og-2026-08-10).</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Olimpo Gold</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Olimpo Gold</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Olimpo Gold</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>NPC Team</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>NPC Team</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>NPC Team</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:36:32.706040Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR15" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>eb53910bc62343f1</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:36:45.039622Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T01:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>75257</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>FUSION X</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>MYVRA GC</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.750891</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>0.110603</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-myvgc-fsnx-2026-08-11).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>FUSION X</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>FUSION X</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>FUSION X</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>MYVRA GC</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>MYVRA GC</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>MYVRA GC</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:36:36.768051Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>ad7e3212cc9a4377</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:36:45.039622Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>77309</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Dragon Ranger Gaming</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Trace Esports</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.521278</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>0.130653</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>85</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-11T16:30:37.306342Z</t>
+        </is>
+      </c>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-te-drg-2026-08-11).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>Dragon Ranger Gaming</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>Dragon Ranger Gaming</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>Dragon Ranger Gaming</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>Trace Esports</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>Trace Esports</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>Trace Esports</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-10T16:36:39.099981Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>cf3f1e94a7fd4909</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:37:16.864247Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>76905</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.601267</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.291669</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="AA18" s="28" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB18" s="28" t="n">
+        <v>0.000402</v>
+      </c>
+      <c r="AC18" s="30" t="n">
+        <v>2.7875</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:41:06.337138Z</t>
+        </is>
+      </c>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-valorant-sge-gm-2026-08-12).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>544d1cd34df6c8d22913af55b6e1b019f8a76a060474a2450daa185b339b6d8d</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>544d1cd34df6c8d22913af55b6e1b019f8a76a060474a2450daa185b339b6d8d</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:37:09.887094Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BR18" s="28" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>57e3e8d6743c492f</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:36.247336Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>76535</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Team Heretics</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.642814</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>0.062982</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="n"/>
+      <c r="W19" s="26" t="n"/>
+      <c r="X19" s="26" t="n"/>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n"/>
+      <c r="AD19" s="24" t="n"/>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-valorant-th-navi-2026-08-12).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Natus Vincere</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>Team Heretics</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>Team Heretics</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>Team Heretics</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:26.441713Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>43aa834f71984e7b</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:36.247336Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T23:30:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>78205</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.519891</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>0.189858</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="n"/>
+      <c r="W20" s="26" t="n"/>
+      <c r="X20" s="26" t="n"/>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n"/>
+      <c r="AD20" s="24" t="n"/>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-valorant-mvs-spi-2026-08-12).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>The Spiders</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>MVSK Secret</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:30.097634Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>dbc6d13bad474b15</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:36.247336Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>77171</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>ONSIDE GAMING</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.578341</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>0.158173</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-krx-osg-2026-08-13).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>ONSIDE GAMING</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>ONSIDE GAMING</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>ONSIDE GAMING</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom DRX</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:30.751879Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>9d4ef0378675480d</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:36.247336Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>77227</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Sharper Esport</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Rex Regum Qeon</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>212</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.320513</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.536314</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>0.215801</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3200 (market_slug=aec-valorant-rrq-spe-2026-08-13).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>Sharper Esport</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Sharper Esport</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Sharper Esport</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>Rex Regum Qeon</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Rex Regum Qeon</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Rex Regum Qeon</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:31.632005Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>212</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.320513</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>33afde8b41694dbd</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:36.247336Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>77546</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates GC</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.689042</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.029178</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="26" t="n"/>
+      <c r="X23" s="26" t="n"/>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n"/>
+      <c r="AD23" s="24" t="n"/>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-fso-m8gc-2026-08-13).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates GC</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates GC</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>Gentle Mates GC</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>FOKUS Sakura</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:34.768410Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>056633cd5d054196</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:36.247336Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>77923</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>KRÜ Esports</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.727042</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>0.327042</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-valorant-kr-bst-2026-08-13).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>KRÜ Esports</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>KRÜ Esports</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>KRÜ Esports</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:35.503645Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>19436ce53cdb4af4</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:36.247336Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-14T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>78063</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>M80</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Team Envy</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.764164</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-valorant-nv-m80-2026-08-14).</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>M80</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>M80</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>M80</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>Team Envy</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Team Envy</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Team Envy</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:36.244313Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/gated_research/valorant.xlsx
+++ b/data/gated_research/valorant.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS25" headerRowCount="1">
-  <autoFilter ref="A1:CS25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS26" headerRowCount="1">
+  <autoFilter ref="A1:CS26"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$25)</f>
+        <f>COUNTA('Picks'!$A$2:$A$26)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$25,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$26,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$25,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$26,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")/(COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"win")+COUNTIFS('Picks'!$BX$2:$BX$25,"&gt;0",'Picks'!$V$2:$V$25,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")/(COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"win")+COUNTIFS('Picks'!$BX$2:$BX$26,"&gt;0",'Picks'!$V$2:$V$26,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$25)/SUM('Picks'!$BX$2:$BX$25),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$26)/SUM('Picks'!$BX$2:$BX$26),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$25)</f>
+        <f>SUM('Picks'!$BY$2:$BY$26)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$25,"&lt;&gt;",'Picks'!$AB$2:$AB$25),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$26,"&lt;&gt;",'Picks'!$AB$2:$AB$26),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$25,'Picks'!$AM$2:$AM$25,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$26,'Picks'!$AM$2:$AM$26,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A14,'Picks'!$U$2:$U$25,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A14,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A15,'Picks'!$U$2:$U$25,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A15,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled",'Picks'!$V$2:$V$25,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled",'Picks'!$V$2:$V$26,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$25,'Picks'!$H$2:$H$25,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$26,'Picks'!$H$2:$H$26,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$25,'Picks'!$H$2:$H$25,$A16,'Picks'!$U$2:$U$25,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$26,'Picks'!$H$2:$H$26,$A16,'Picks'!$U$2:$U$26,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS25"/>
+  <dimension ref="A1:CS26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1606,22 +1606,22 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>4a93f1c3a9db405a</t>
+          <t>993252575c7e4976</t>
         </is>
       </c>
       <c r="B2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T10:46:58.818420Z</t>
+          <t>2026-08-04T16:54:18.134287Z</t>
         </is>
       </c>
       <c r="C2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T11:00:00Z</t>
+          <t>2026-08-04T18:00:00Z</t>
         </is>
       </c>
       <c r="D2" s="24" t="inlineStr">
         <is>
-          <t>64807</t>
+          <t>68698</t>
         </is>
       </c>
       <c r="E2" s="24" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="F2" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="G2" s="24" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="H2" s="24" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="I2" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J2" s="25" t="n"/>
@@ -1656,30 +1656,30 @@
         </is>
       </c>
       <c r="L2" s="26" t="n">
-        <v>203</v>
+        <v>-163</v>
       </c>
       <c r="M2" s="27" t="n">
-        <v>3.03</v>
+        <v>1.613497</v>
       </c>
       <c r="N2" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.619772</v>
       </c>
       <c r="O2" s="28" t="n">
-        <v>0.574963</v>
+        <v>0.64657</v>
       </c>
       <c r="P2" s="28" t="n"/>
       <c r="Q2" s="28" t="n">
-        <v>0.24493</v>
+        <v>0.026798</v>
       </c>
       <c r="R2" s="26" t="n">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="S2" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T2" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U2" s="24" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="V2" s="24" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W2" s="26" t="n">
@@ -1700,25 +1700,25 @@
       </c>
       <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n">
-        <v>194</v>
+        <v>-170</v>
       </c>
       <c r="AA2" s="28" t="n">
-        <v>0.34</v>
+        <v>0.63</v>
       </c>
       <c r="AB2" s="28" t="n">
-        <v>0.009967</v>
+        <v>0.010228</v>
       </c>
       <c r="AC2" s="30" t="n">
-        <v>2.5375</v>
+        <v>-1.75</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T13:39:00.824188Z</t>
+          <t>2026-08-04T22:00:12.102961Z</t>
         </is>
       </c>
       <c r="AE2" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-valorant-ge-geng-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-skn-tmo-2026-08-04).</t>
         </is>
       </c>
       <c r="AF2" s="31" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AG2" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH2" s="24" t="n"/>
@@ -1759,32 +1759,32 @@
       </c>
       <c r="AP2" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AQ2" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AR2" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AS2" s="24" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AT2" s="24" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AU2" s="24" t="inlineStr">
         <is>
-          <t>Global Esports</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AV2" s="24" t="n"/>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="BA2" s="24" t="inlineStr">
         <is>
-          <t>316f14757ba7b67513d2e43f0e5432e02d1d1af04a03ed2b8a0b070efbf6c94e</t>
+          <t>2a3a3c0d919df15db76d78df508a996bd8f684ec881c5b644b1e53da56868427</t>
         </is>
       </c>
       <c r="BB2" s="24" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="BC2" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD2" s="24" t="inlineStr">
         <is>
-          <t>316f14757ba7b67513d2e43f0e5432e02d1d1af04a03ed2b8a0b070efbf6c94e</t>
+          <t>2a3a3c0d919df15db76d78df508a996bd8f684ec881c5b644b1e53da56868427</t>
         </is>
       </c>
       <c r="BE2" s="24" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="BG2" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH2" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T10:46:53.940374Z</t>
+          <t>2026-08-04T16:54:14.515679Z</t>
         </is>
       </c>
       <c r="BI2" s="24" t="inlineStr">
@@ -1847,22 +1847,22 @@
       </c>
       <c r="BJ2" s="25" t="n"/>
       <c r="BK2" s="26" t="n">
-        <v>203</v>
+        <v>-163</v>
       </c>
       <c r="BL2" s="27" t="n">
-        <v>3.03</v>
+        <v>1.613497</v>
       </c>
       <c r="BM2" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.619772</v>
       </c>
       <c r="BN2" s="28" t="n"/>
       <c r="BO2" s="28" t="n"/>
       <c r="BP2" s="25" t="n"/>
       <c r="BQ2" s="27" t="n">
-        <v>2.94</v>
+        <v>1.588235</v>
       </c>
       <c r="BR2" s="28" t="n">
-        <v>0.34</v>
+        <v>0.63</v>
       </c>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
@@ -1890,27 +1890,31 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
-      <c r="CS2" s="24" t="n"/>
+      <c r="CS2" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>aa60324bb524406d</t>
+          <t>fbbd225f128542cc</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T13:44:08.052962Z</t>
+          <t>2026-08-05T04:38:20.842798Z</t>
         </is>
       </c>
       <c r="C3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T15:00:00Z</t>
+          <t>2026-08-05T10:00:00Z</t>
         </is>
       </c>
       <c r="D3" s="24" t="inlineStr">
         <is>
-          <t>64940</t>
+          <t>69540</t>
         </is>
       </c>
       <c r="E3" s="24" t="inlineStr">
@@ -1920,12 +1924,12 @@
       </c>
       <c r="F3" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>KeepBest Gaming</t>
         </is>
       </c>
       <c r="G3" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>TEC Esports</t>
         </is>
       </c>
       <c r="H3" s="24" t="inlineStr">
@@ -1935,7 +1939,7 @@
       </c>
       <c r="I3" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J3" s="25" t="n"/>
@@ -1945,30 +1949,30 @@
         </is>
       </c>
       <c r="L3" s="26" t="n">
-        <v>-127</v>
+        <v>122</v>
       </c>
       <c r="M3" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.22</v>
       </c>
       <c r="N3" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.45045</v>
       </c>
       <c r="O3" s="28" t="n">
-        <v>0.589785</v>
+        <v>0.575198</v>
       </c>
       <c r="P3" s="28" t="n"/>
       <c r="Q3" s="28" t="n">
-        <v>0.030314</v>
+        <v>0.124748</v>
       </c>
       <c r="R3" s="26" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="S3" s="29" t="n">
         <v>1.25</v>
       </c>
       <c r="T3" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U3" s="24" t="inlineStr">
@@ -1978,7 +1982,7 @@
       </c>
       <c r="V3" s="24" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W3" s="26" t="n">
@@ -1989,25 +1993,25 @@
       </c>
       <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n">
-        <v>-127</v>
+        <v>122</v>
       </c>
       <c r="AA3" s="28" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="AB3" s="28" t="n">
-        <v>0.000529</v>
+        <v>-0.00045</v>
       </c>
       <c r="AC3" s="30" t="n">
-        <v>0.9843</v>
+        <v>-1.25</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T19:51:30.853090Z</t>
+          <t>2026-08-05T13:52:01.477710Z</t>
         </is>
       </c>
       <c r="AE3" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-valorant-bbl-gm-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
         </is>
       </c>
       <c r="AF3" s="31" t="inlineStr">
@@ -2017,7 +2021,7 @@
       </c>
       <c r="AG3" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH3" s="24" t="n"/>
@@ -2048,32 +2052,32 @@
       </c>
       <c r="AP3" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>KeepBest Gaming</t>
         </is>
       </c>
       <c r="AQ3" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>KeepBest Gaming</t>
         </is>
       </c>
       <c r="AR3" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>KeepBest Gaming</t>
         </is>
       </c>
       <c r="AS3" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>TEC Esports</t>
         </is>
       </c>
       <c r="AT3" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>TEC Esports</t>
         </is>
       </c>
       <c r="AU3" s="24" t="inlineStr">
         <is>
-          <t>BBL Esports</t>
+          <t>TEC Esports</t>
         </is>
       </c>
       <c r="AV3" s="24" t="n"/>
@@ -2091,7 +2095,7 @@
       </c>
       <c r="BA3" s="24" t="inlineStr">
         <is>
-          <t>139f8fd81efcd2fb54fc3e158052d3e9c04fc7442a0b372b18e645e84996b74c</t>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
         </is>
       </c>
       <c r="BB3" s="24" t="inlineStr">
@@ -2101,12 +2105,12 @@
       </c>
       <c r="BC3" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD3" s="24" t="inlineStr">
         <is>
-          <t>139f8fd81efcd2fb54fc3e158052d3e9c04fc7442a0b372b18e645e84996b74c</t>
+          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
         </is>
       </c>
       <c r="BE3" s="24" t="inlineStr">
@@ -2121,12 +2125,12 @@
       </c>
       <c r="BG3" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH3" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T13:44:03.465992Z</t>
+          <t>2026-08-05T04:38:10.028876Z</t>
         </is>
       </c>
       <c r="BI3" s="24" t="inlineStr">
@@ -2136,22 +2140,22 @@
       </c>
       <c r="BJ3" s="25" t="n"/>
       <c r="BK3" s="26" t="n">
-        <v>-127</v>
+        <v>122</v>
       </c>
       <c r="BL3" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.22</v>
       </c>
       <c r="BM3" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.45045</v>
       </c>
       <c r="BN3" s="28" t="n"/>
       <c r="BO3" s="28" t="n"/>
       <c r="BP3" s="25" t="n"/>
       <c r="BQ3" s="27" t="n">
-        <v>1.787402</v>
+        <v>2.22</v>
       </c>
       <c r="BR3" s="28" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
@@ -2179,27 +2183,31 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
-      <c r="CS3" s="24" t="n"/>
+      <c r="CS3" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>3ed05efb0fb74970</t>
+          <t>4afe1804253940e0</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T23:55:04.278999Z</t>
+          <t>2026-08-06T00:24:39.463638Z</t>
         </is>
       </c>
       <c r="C4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T00:00:00Z</t>
+          <t>2026-08-06T15:00:00Z</t>
         </is>
       </c>
       <c r="D4" s="24" t="inlineStr">
         <is>
-          <t>66659</t>
+          <t>70724</t>
         </is>
       </c>
       <c r="E4" s="24" t="inlineStr">
@@ -2209,12 +2217,12 @@
       </c>
       <c r="F4" s="24" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="G4" s="24" t="inlineStr">
         <is>
-          <t>Leviatán Esports</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="H4" s="24" t="inlineStr">
@@ -2224,7 +2232,7 @@
       </c>
       <c r="I4" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J4" s="25" t="n"/>
@@ -2234,30 +2242,30 @@
         </is>
       </c>
       <c r="L4" s="26" t="n">
-        <v>-138</v>
+        <v>138</v>
       </c>
       <c r="M4" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.38</v>
       </c>
       <c r="N4" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.420168</v>
       </c>
       <c r="O4" s="28" t="n">
-        <v>0.608104</v>
+        <v>0.695761</v>
       </c>
       <c r="P4" s="28" t="n"/>
       <c r="Q4" s="28" t="n">
-        <v>0.028272</v>
+        <v>0.275593</v>
       </c>
       <c r="R4" s="26" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="S4" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T4" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U4" s="24" t="inlineStr">
@@ -2271,32 +2279,26 @@
         </is>
       </c>
       <c r="W4" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="X4" s="26" t="n">
-        <v>0</v>
-      </c>
       <c r="Y4" s="25" t="n"/>
-      <c r="Z4" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="AA4" s="28" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="AB4" s="28" t="n">
-        <v>0.000168</v>
-      </c>
+      <c r="Z4" s="26" t="n"/>
+      <c r="AA4" s="28" t="n"/>
+      <c r="AB4" s="28" t="n"/>
       <c r="AC4" s="30" t="n">
-        <v>-1.5</v>
+        <v>-2</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T04:26:24.624792Z</t>
+          <t>2026-08-06T18:57:16.552761Z</t>
         </is>
       </c>
       <c r="AE4" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-valorant-lev-nrg-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-gx-sge-2026-08-06).</t>
         </is>
       </c>
       <c r="AF4" s="31" t="inlineStr">
@@ -2337,32 +2339,32 @@
       </c>
       <c r="AP4" s="24" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AQ4" s="24" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AR4" s="24" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AS4" s="24" t="inlineStr">
         <is>
-          <t>Leviatán Esports</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="AT4" s="24" t="inlineStr">
         <is>
-          <t>Leviatán Esports</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="AU4" s="24" t="inlineStr">
         <is>
-          <t>Leviatán Esports</t>
+          <t>GIANTX</t>
         </is>
       </c>
       <c r="AV4" s="24" t="n"/>
@@ -2380,7 +2382,7 @@
       </c>
       <c r="BA4" s="24" t="inlineStr">
         <is>
-          <t>4e9833fa3108f9876de728871233bbb749924096e4b6984ae7ee11ff9d8be0d1</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BB4" s="24" t="inlineStr">
@@ -2390,12 +2392,12 @@
       </c>
       <c r="BC4" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD4" s="24" t="inlineStr">
         <is>
-          <t>4e9833fa3108f9876de728871233bbb749924096e4b6984ae7ee11ff9d8be0d1</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BE4" s="24" t="inlineStr">
@@ -2410,12 +2412,12 @@
       </c>
       <c r="BG4" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T23:55:01.262855Z</t>
+          <t>2026-08-06T00:24:37.569959Z</t>
         </is>
       </c>
       <c r="BI4" s="24" t="inlineStr">
@@ -2425,23 +2427,19 @@
       </c>
       <c r="BJ4" s="25" t="n"/>
       <c r="BK4" s="26" t="n">
-        <v>-138</v>
+        <v>138</v>
       </c>
       <c r="BL4" s="27" t="n">
-        <v>1.724638</v>
+        <v>2.38</v>
       </c>
       <c r="BM4" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.420168</v>
       </c>
       <c r="BN4" s="28" t="n"/>
       <c r="BO4" s="28" t="n"/>
       <c r="BP4" s="25" t="n"/>
-      <c r="BQ4" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="BR4" s="28" t="n">
-        <v>0.58</v>
-      </c>
+      <c r="BQ4" s="27" t="n"/>
+      <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
       <c r="BU4" s="25" t="n"/>
@@ -2468,27 +2466,31 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
-      <c r="CS4" s="24" t="n"/>
+      <c r="CS4" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>9be1b88469434301</t>
+          <t>9ac66283b1f0467b</t>
         </is>
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:42.752833Z</t>
+          <t>2026-08-06T00:24:39.463638Z</t>
         </is>
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:00:00Z</t>
+          <t>2026-08-06T18:00:00Z</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>66788</t>
+          <t>70912</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -2498,12 +2500,12 @@
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="G5" s="24" t="inlineStr">
         <is>
-          <t>VARREL</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="H5" s="24" t="inlineStr">
@@ -2523,30 +2525,30 @@
         </is>
       </c>
       <c r="L5" s="26" t="n">
-        <v>-150</v>
+        <v>178</v>
       </c>
       <c r="M5" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.78</v>
       </c>
       <c r="N5" s="28" t="n">
-        <v>0.6</v>
+        <v>0.359712</v>
       </c>
       <c r="O5" s="28" t="n">
-        <v>0.676998</v>
+        <v>0.563029</v>
       </c>
       <c r="P5" s="28" t="n"/>
       <c r="Q5" s="28" t="n">
-        <v>0.076998</v>
+        <v>0.203317</v>
       </c>
       <c r="R5" s="26" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="S5" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T5" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U5" s="24" t="inlineStr">
@@ -2556,36 +2558,30 @@
       </c>
       <c r="V5" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W5" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="X5" s="26" t="n">
-        <v>1</v>
-      </c>
       <c r="Y5" s="25" t="n"/>
-      <c r="Z5" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="AA5" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AB5" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z5" s="26" t="n"/>
+      <c r="AA5" s="28" t="n"/>
+      <c r="AB5" s="28" t="n"/>
       <c r="AC5" s="30" t="n">
-        <v>-1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T11:45:35.969857Z</t>
+          <t>2026-08-07T06:01:54.163030Z</t>
         </is>
       </c>
       <c r="AE5" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-valorant-var-krx-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-valorant-navi-jl-2026-08-06).</t>
         </is>
       </c>
       <c r="AF5" s="31" t="inlineStr">
@@ -2595,7 +2591,7 @@
       </c>
       <c r="AG5" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH5" s="24" t="n"/>
@@ -2626,32 +2622,32 @@
       </c>
       <c r="AP5" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AQ5" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AR5" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AS5" s="24" t="inlineStr">
         <is>
-          <t>VARREL</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AT5" s="24" t="inlineStr">
         <is>
-          <t>VARREL</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AU5" s="24" t="inlineStr">
         <is>
-          <t>VARREL</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AV5" s="24" t="n"/>
@@ -2669,7 +2665,7 @@
       </c>
       <c r="BA5" s="24" t="inlineStr">
         <is>
-          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BB5" s="24" t="inlineStr">
@@ -2679,12 +2675,12 @@
       </c>
       <c r="BC5" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD5" s="24" t="inlineStr">
         <is>
-          <t>f7ffe38e2a3b5170b3b9b10a398835b3cdb1a4df5cfd051a3ffa836bf9de2c76</t>
+          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
         </is>
       </c>
       <c r="BE5" s="24" t="inlineStr">
@@ -2699,12 +2695,12 @@
       </c>
       <c r="BG5" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH5" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:34.729300Z</t>
+          <t>2026-08-06T00:24:38.040365Z</t>
         </is>
       </c>
       <c r="BI5" s="24" t="inlineStr">
@@ -2714,23 +2710,19 @@
       </c>
       <c r="BJ5" s="25" t="n"/>
       <c r="BK5" s="26" t="n">
-        <v>-150</v>
+        <v>178</v>
       </c>
       <c r="BL5" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.78</v>
       </c>
       <c r="BM5" s="28" t="n">
-        <v>0.6</v>
+        <v>0.359712</v>
       </c>
       <c r="BN5" s="28" t="n"/>
       <c r="BO5" s="28" t="n"/>
       <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="BR5" s="28" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="BQ5" s="27" t="n"/>
+      <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
       <c r="BU5" s="25" t="n"/>
@@ -2757,27 +2749,31 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
-      <c r="CS5" s="24" t="n"/>
+      <c r="CS5" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
         <is>
-          <t>ad8fa896c5344f29</t>
+          <t>33fe14e66f0c4a77</t>
         </is>
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T13:30:41.417037Z</t>
+          <t>2026-08-06T19:00:18.001858Z</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T15:00:00Z</t>
+          <t>2026-08-06T21:00:00Z</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>67569</t>
+          <t>71315</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -2787,12 +2783,12 @@
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>FURIA Esports</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="H6" s="24" t="inlineStr">
@@ -2812,30 +2808,30 @@
         </is>
       </c>
       <c r="L6" s="26" t="n">
-        <v>-163</v>
+        <v>117</v>
       </c>
       <c r="M6" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.17</v>
       </c>
       <c r="N6" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.460829</v>
       </c>
       <c r="O6" s="28" t="n">
-        <v>0.765423</v>
+        <v>0.615411</v>
       </c>
       <c r="P6" s="28" t="n"/>
       <c r="Q6" s="28" t="n">
-        <v>0.145651</v>
+        <v>0.154582</v>
       </c>
       <c r="R6" s="26" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="S6" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T6" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U6" s="24" t="inlineStr">
@@ -2845,36 +2841,36 @@
       </c>
       <c r="V6" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="26" t="n">
         <v>1</v>
-      </c>
-      <c r="X6" s="26" t="n">
-        <v>0</v>
       </c>
       <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n">
-        <v>-163</v>
+        <v>117</v>
       </c>
       <c r="AA6" s="28" t="n">
-        <v>0.62</v>
+        <v>0.46</v>
       </c>
       <c r="AB6" s="28" t="n">
-        <v>0.000228</v>
+        <v>-0.000829</v>
       </c>
       <c r="AC6" s="30" t="n">
-        <v>-2</v>
+        <v>1.755</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T17:06:06.463819Z</t>
+          <t>2026-08-07T06:01:55.454308Z</t>
         </is>
       </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-skn-fso-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-eg-fur-2026-08-06).</t>
         </is>
       </c>
       <c r="AF6" s="31" t="inlineStr">
@@ -2884,7 +2880,7 @@
       </c>
       <c r="AG6" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH6" s="24" t="n"/>
@@ -2915,32 +2911,32 @@
       </c>
       <c r="AP6" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>FURIA Esports</t>
         </is>
       </c>
       <c r="AQ6" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>FURIA Esports</t>
         </is>
       </c>
       <c r="AR6" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>FURIA Esports</t>
         </is>
       </c>
       <c r="AS6" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="AT6" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="AU6" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Evil Geniuses</t>
         </is>
       </c>
       <c r="AV6" s="24" t="n"/>
@@ -2958,7 +2954,7 @@
       </c>
       <c r="BA6" s="24" t="inlineStr">
         <is>
-          <t>afe2fffd3c666e0d8f9040dcc6dedae587629fd14dee7043c87557d9d9d9e6e5</t>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
         </is>
       </c>
       <c r="BB6" s="24" t="inlineStr">
@@ -2968,12 +2964,12 @@
       </c>
       <c r="BC6" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD6" s="24" t="inlineStr">
         <is>
-          <t>afe2fffd3c666e0d8f9040dcc6dedae587629fd14dee7043c87557d9d9d9e6e5</t>
+          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
         </is>
       </c>
       <c r="BE6" s="24" t="inlineStr">
@@ -2988,12 +2984,12 @@
       </c>
       <c r="BG6" s="24" t="inlineStr">
         <is>
-          <t>valorant-tiered-elo-v5</t>
+          <t>valorant-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH6" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T13:30:33.637118Z</t>
+          <t>2026-08-06T19:00:13.149018Z</t>
         </is>
       </c>
       <c r="BI6" s="24" t="inlineStr">
@@ -3003,22 +2999,22 @@
       </c>
       <c r="BJ6" s="25" t="n"/>
       <c r="BK6" s="26" t="n">
-        <v>-163</v>
+        <v>117</v>
       </c>
       <c r="BL6" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.17</v>
       </c>
       <c r="BM6" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.460829</v>
       </c>
       <c r="BN6" s="28" t="n"/>
       <c r="BO6" s="28" t="n"/>
       <c r="BP6" s="25" t="n"/>
       <c r="BQ6" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.17</v>
       </c>
       <c r="BR6" s="28" t="n">
-        <v>0.62</v>
+        <v>0.46</v>
       </c>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
@@ -3055,22 +3051,22 @@
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
-          <t>993252575c7e4976</t>
+          <t>ccd5f17eb0c54739</t>
         </is>
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T16:54:18.134287Z</t>
+          <t>2026-08-07T09:11:28.912966Z</t>
         </is>
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:00:00Z</t>
+          <t>2026-08-07T11:00:00Z</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>68698</t>
+          <t>71752</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -3080,12 +3076,12 @@
       </c>
       <c r="F7" s="24" t="inlineStr">
         <is>
-          <t>Twisted Minds Orchid</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="G7" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
@@ -3105,26 +3101,26 @@
         </is>
       </c>
       <c r="L7" s="26" t="n">
-        <v>-163</v>
+        <v>-156</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.641026</v>
       </c>
       <c r="N7" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.609375</v>
       </c>
       <c r="O7" s="28" t="n">
-        <v>0.64657</v>
+        <v>0.781485</v>
       </c>
       <c r="P7" s="28" t="n"/>
       <c r="Q7" s="28" t="n">
-        <v>0.026798</v>
+        <v>0.17211</v>
       </c>
       <c r="R7" s="26" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="S7" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T7" s="24" t="inlineStr">
         <is>
@@ -3138,36 +3134,36 @@
       </c>
       <c r="V7" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="26" t="n">
         <v>1</v>
-      </c>
-      <c r="X7" s="26" t="n">
-        <v>0</v>
       </c>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n">
-        <v>-170</v>
+        <v>-156</v>
       </c>
       <c r="AA7" s="28" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="AB7" s="28" t="n">
-        <v>0.010228</v>
+        <v>0.000625</v>
       </c>
       <c r="AC7" s="30" t="n">
-        <v>-1.75</v>
+        <v>1.2821</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T22:00:12.102961Z</t>
+          <t>2026-08-07T15:20:06.633818Z</t>
         </is>
       </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-valorant-skn-tmo-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-valorant-geng-fs-2026-08-07).</t>
         </is>
       </c>
       <c r="AF7" s="31" t="inlineStr">
@@ -3177,7 +3173,7 @@
       </c>
       <c r="AG7" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH7" s="24" t="n"/>
@@ -3208,32 +3204,32 @@
       </c>
       <c r="AP7" s="24" t="inlineStr">
         <is>
-          <t>Twisted Minds Orchid</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="AQ7" s="24" t="inlineStr">
         <is>
-          <t>Twisted Minds Orchid</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="AR7" s="24" t="inlineStr">
         <is>
-          <t>Twisted Minds Orchid</t>
+          <t>FULL SENSE</t>
         </is>
       </c>
       <c r="AS7" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AT7" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AU7" s="24" t="inlineStr">
         <is>
-          <t>SK Nebula</t>
+          <t>Gen.G Esports</t>
         </is>
       </c>
       <c r="AV7" s="24" t="n"/>
@@ -3251,7 +3247,7 @@
       </c>
       <c r="BA7" s="24" t="inlineStr">
         <is>
-          <t>2a3a3c0d919df15db76d78df508a996bd8f684ec881c5b644b1e53da56868427</t>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
         </is>
       </c>
       <c r="BB7" s="24" t="inlineStr">
@@ -3266,7 +3262,7 @@
       </c>
       <c r="BD7" s="24" t="inlineStr">
         <is>
-          <t>2a3a3c0d919df15db76d78df508a996bd8f684ec881c5b644b1e53da56868427</t>
+          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
         </is>
       </c>
       <c r="BE7" s="24" t="inlineStr">
@@ -3286,7 +3282,7 @@
       </c>
       <c r="BH7" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T16:54:14.515679Z</t>
+          <t>2026-08-07T09:11:21.351080Z</t>
         </is>
       </c>
       <c r="BI7" s="24" t="inlineStr">
@@ -3296,22 +3292,22 @@
       </c>
       <c r="BJ7" s="25" t="n"/>
       <c r="BK7" s="26" t="n">
-        <v>-163</v>
+        <v>-156</v>
       </c>
       <c r="BL7" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.641026</v>
       </c>
       <c r="BM7" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.609375</v>
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
       <c r="BP7" s="25" t="n"/>
       <c r="BQ7" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.641026</v>
       </c>
       <c r="BR7" s="28" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
@@ -3348,22 +3344,22 @@
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>fbbd225f128542cc</t>
+          <t>94a64e146f5740da</t>
         </is>
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:20.842798Z</t>
+          <t>2026-08-07T15:24:00.757019Z</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T10:00:00Z</t>
+          <t>2026-08-07T18:00:00Z</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>69540</t>
+          <t>72078</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -3373,12 +3369,12 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>KeepBest Gaming</t>
+          <t>Enterprise Esports</t>
         </is>
       </c>
       <c r="G8" s="24" t="inlineStr">
         <is>
-          <t>TEC Esports</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
@@ -3398,26 +3394,26 @@
         </is>
       </c>
       <c r="L8" s="26" t="n">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>2.22</v>
+        <v>2.78</v>
       </c>
       <c r="N8" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.359712</v>
       </c>
       <c r="O8" s="28" t="n">
-        <v>0.575198</v>
+        <v>0.743264</v>
       </c>
       <c r="P8" s="28" t="n"/>
       <c r="Q8" s="28" t="n">
-        <v>0.124748</v>
+        <v>0.383552</v>
       </c>
       <c r="R8" s="26" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="S8" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T8" s="24" t="inlineStr">
         <is>
@@ -3431,36 +3427,36 @@
       </c>
       <c r="V8" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" s="26" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" s="26" t="n">
-        <v>1</v>
       </c>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="AA8" s="28" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="AB8" s="28" t="n">
-        <v>-0.00045</v>
+        <v>0.000288</v>
       </c>
       <c r="AC8" s="30" t="n">
-        <v>-1.25</v>
+        <v>3.56</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T13:52:01.477710Z</t>
+          <t>2026-08-07T21:55:39.052370Z</t>
         </is>
       </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-valorant-tec-kbg-2026-08-05).</t>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-valorant-fnc-ep-2026-08-07).</t>
         </is>
       </c>
       <c r="AF8" s="31" t="inlineStr">
@@ -3470,7 +3466,7 @@
       </c>
       <c r="AG8" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH8" s="24" t="n"/>
@@ -3501,32 +3497,32 @@
       </c>
       <c r="AP8" s="24" t="inlineStr">
         <is>
-          <t>KeepBest Gaming</t>
+          <t>Enterprise Esports</t>
         </is>
       </c>
       <c r="AQ8" s="24" t="inlineStr">
         <is>
-          <t>KeepBest Gaming</t>
+          <t>Enterprise Esports</t>
         </is>
       </c>
       <c r="AR8" s="24" t="inlineStr">
         <is>
-          <t>KeepBest Gaming</t>
+          <t>Enterprise Esports</t>
         </is>
       </c>
       <c r="AS8" s="24" t="inlineStr">
         <is>
-          <t>TEC Esports</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AT8" s="24" t="inlineStr">
         <is>
-          <t>TEC Esports</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AU8" s="24" t="inlineStr">
         <is>
-          <t>TEC Esports</t>
+          <t>Fnatic</t>
         </is>
       </c>
       <c r="AV8" s="24" t="n"/>
@@ -3544,7 +3540,7 @@
       </c>
       <c r="BA8" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
         </is>
       </c>
       <c r="BB8" s="24" t="inlineStr">
@@ -3559,7 +3555,7 @@
       </c>
       <c r="BD8" s="24" t="inlineStr">
         <is>
-          <t>186664e065cb2f3876c035d1fafb20f41e71ec1c33421a9590b0fc42032b5796</t>
+          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
         </is>
       </c>
       <c r="BE8" s="24" t="inlineStr">
@@ -3579,7 +3575,7 @@
       </c>
       <c r="BH8" s="24" t="inlineStr">
         <is>
-          <t>2026-08-05T04:38:10.028876Z</t>
+          <t>2026-08-07T15:23:54.113763Z</t>
         </is>
       </c>
       <c r="BI8" s="24" t="inlineStr">
@@ -3589,22 +3585,22 @@
       </c>
       <c r="BJ8" s="25" t="n"/>
       <c r="BK8" s="26" t="n">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="BL8" s="27" t="n">
-        <v>2.22</v>
+        <v>2.78</v>
       </c>
       <c r="BM8" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.359712</v>
       </c>
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
       <c r="BP8" s="25" t="n"/>
       <c r="BQ8" s="27" t="n">
-        <v>2.22</v>
+        <v>2.78</v>
       </c>
       <c r="BR8" s="28" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
@@ -3641,22 +3637,22 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>4afe1804253940e0</t>
+          <t>e501297caddc4e51</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T00:24:39.463638Z</t>
+          <t>2026-08-09T17:08:20.055519Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T15:00:00Z</t>
+          <t>2026-08-09T18:00:00Z</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>70724</t>
+          <t>74609</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3666,12 +3662,12 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Enterprise Esports</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -3691,20 +3687,20 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.4</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.695761</v>
+        <v>0.804725</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.275593</v>
+        <v>0.404725</v>
       </c>
       <c r="R9" s="26" t="n">
         <v>100</v>
@@ -3724,30 +3720,36 @@
       </c>
       <c r="V9" s="24" t="inlineStr">
         <is>
-          <t>loss</t>
+          <t>win</t>
         </is>
       </c>
       <c r="W9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="X9" s="26" t="n">
-        <v>1</v>
-      </c>
       <c r="Y9" s="25" t="n"/>
-      <c r="Z9" s="26" t="n"/>
-      <c r="AA9" s="28" t="n"/>
-      <c r="AB9" s="28" t="n"/>
+      <c r="Z9" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA9" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB9" s="28" t="n">
+        <v>0</v>
+      </c>
       <c r="AC9" s="30" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T18:57:16.552761Z</t>
+          <t>2026-08-09T20:26:25.086079Z</t>
         </is>
       </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-gx-sge-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-valorant-gm-ep-2026-08-09).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3757,7 +3759,7 @@
       </c>
       <c r="AG9" s="24" t="inlineStr">
         <is>
-          <t>review_required</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="AH9" s="24" t="n"/>
@@ -3788,32 +3790,32 @@
       </c>
       <c r="AP9" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Enterprise Esports</t>
         </is>
       </c>
       <c r="AQ9" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Enterprise Esports</t>
         </is>
       </c>
       <c r="AR9" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Enterprise Esports</t>
         </is>
       </c>
       <c r="AS9" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="AT9" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="AU9" s="24" t="inlineStr">
         <is>
-          <t>GIANTX</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="AV9" s="24" t="n"/>
@@ -3831,7 +3833,7 @@
       </c>
       <c r="BA9" s="24" t="inlineStr">
         <is>
-          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+          <t>43316dd49e7f9b1a20757c6d2b94b720f27a77b2c5fd90af5fff6a8c8dacabc4</t>
         </is>
       </c>
       <c r="BB9" s="24" t="inlineStr">
@@ -3846,7 +3848,7 @@
       </c>
       <c r="BD9" s="24" t="inlineStr">
         <is>
-          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+          <t>43316dd49e7f9b1a20757c6d2b94b720f27a77b2c5fd90af5fff6a8c8dacabc4</t>
         </is>
       </c>
       <c r="BE9" s="24" t="inlineStr">
@@ -3866,7 +3868,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T00:24:37.569959Z</t>
+          <t>2026-08-09T17:08:10.558137Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3876,19 +3878,23 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.4</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
       <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
-      <c r="BR9" s="28" t="n"/>
+      <c r="BQ9" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR9" s="28" t="n">
+        <v>0.4</v>
+      </c>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
       <c r="BU9" s="25" t="n"/>
@@ -3924,22 +3930,22 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>9ac66283b1f0467b</t>
+          <t>7ab28900c23e400a</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T00:24:39.463638Z</t>
+          <t>2026-08-10T16:36:45.039622Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T18:00:00Z</t>
+          <t>2026-08-10T22:00:00Z</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>70912</t>
+          <t>75255</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3949,12 +3955,12 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Olimpo Gold</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>NPC Team</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -3974,20 +3980,20 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.4</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.563029</v>
+        <v>0.559409</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>0.203317</v>
+        <v>0.159409</v>
       </c>
       <c r="R10" s="26" t="n">
         <v>100</v>
@@ -4007,30 +4013,36 @@
       </c>
       <c r="V10" s="24" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="X10" s="26" t="n">
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA10" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB10" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="Y10" s="25" t="n"/>
-      <c r="Z10" s="26" t="n"/>
-      <c r="AA10" s="28" t="n"/>
-      <c r="AB10" s="28" t="n"/>
       <c r="AC10" s="30" t="n">
-        <v>1.78</v>
+        <v>-1</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T06:01:54.163030Z</t>
+          <t>2026-08-11T13:09:08.912134Z</t>
         </is>
       </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-valorant-navi-jl-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-valorant-ntp-og-2026-08-10).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -4040,7 +4052,7 @@
       </c>
       <c r="AG10" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH10" s="24" t="n"/>
@@ -4071,32 +4083,32 @@
       </c>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Olimpo Gold</t>
         </is>
       </c>
       <c r="AQ10" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Olimpo Gold</t>
         </is>
       </c>
       <c r="AR10" s="24" t="inlineStr">
         <is>
-          <t>Joblife</t>
+          <t>Olimpo Gold</t>
         </is>
       </c>
       <c r="AS10" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>NPC Team</t>
         </is>
       </c>
       <c r="AT10" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>NPC Team</t>
         </is>
       </c>
       <c r="AU10" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>NPC Team</t>
         </is>
       </c>
       <c r="AV10" s="24" t="n"/>
@@ -4114,7 +4126,7 @@
       </c>
       <c r="BA10" s="24" t="inlineStr">
         <is>
-          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
         </is>
       </c>
       <c r="BB10" s="24" t="inlineStr">
@@ -4129,7 +4141,7 @@
       </c>
       <c r="BD10" s="24" t="inlineStr">
         <is>
-          <t>4df5f295a2b28e76007c7dffc3ff6e8d7c876b7734ec9c379c78b6dce8cd27b3</t>
+          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
         </is>
       </c>
       <c r="BE10" s="24" t="inlineStr">
@@ -4149,7 +4161,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T00:24:38.040365Z</t>
+          <t>2026-08-10T16:36:32.706040Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -4159,19 +4171,23 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.4</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
       <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
-      <c r="BR10" s="28" t="n"/>
+      <c r="BQ10" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR10" s="28" t="n">
+        <v>0.4</v>
+      </c>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
       <c r="BU10" s="25" t="n"/>
@@ -4207,22 +4223,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>33fe14e66f0c4a77</t>
+          <t>eb53910bc62343f1</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T19:00:18.001858Z</t>
+          <t>2026-08-10T16:36:45.039622Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T21:00:00Z</t>
+          <t>2026-08-11T01:00:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>71315</t>
+          <t>75257</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4232,12 +4248,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>FURIA Esports</t>
+          <t>FUSION X</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>MYVRA GC</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4257,26 +4273,26 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>117</v>
+        <v>-178</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>2.17</v>
+        <v>1.561798</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.640288</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.615411</v>
+        <v>0.750891</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.154582</v>
+        <v>0.110603</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="S11" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T11" s="24" t="inlineStr">
         <is>
@@ -4290,36 +4306,36 @@
       </c>
       <c r="V11" s="24" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" s="26" t="n">
         <v>0</v>
-      </c>
-      <c r="X11" s="26" t="n">
-        <v>1</v>
       </c>
       <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n">
-        <v>117</v>
+        <v>-178</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>0.46</v>
+        <v>0.64</v>
       </c>
       <c r="AB11" s="28" t="n">
-        <v>-0.000829</v>
+        <v>-0.000288</v>
       </c>
       <c r="AC11" s="30" t="n">
-        <v>1.755</v>
+        <v>-2</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T06:01:55.454308Z</t>
+          <t>2026-08-13T05:35:03.453400Z</t>
         </is>
       </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-valorant-eg-fur-2026-08-06).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-myvgc-fsnx-2026-08-11).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4329,7 +4345,7 @@
       </c>
       <c r="AG11" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH11" s="24" t="n"/>
@@ -4360,32 +4376,32 @@
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>FURIA Esports</t>
+          <t>FUSION X</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>FURIA Esports</t>
+          <t>FUSION X</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>FURIA Esports</t>
+          <t>FUSION X</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>MYVRA GC</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>MYVRA GC</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>Evil Geniuses</t>
+          <t>MYVRA GC</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4403,7 +4419,7 @@
       </c>
       <c r="BA11" s="24" t="inlineStr">
         <is>
-          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
+          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
         </is>
       </c>
       <c r="BB11" s="24" t="inlineStr">
@@ -4418,7 +4434,7 @@
       </c>
       <c r="BD11" s="24" t="inlineStr">
         <is>
-          <t>b32c21f8580cb36d2689c3449e18565f3db3f1690f09f65a3c552f717e24b35d</t>
+          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
         </is>
       </c>
       <c r="BE11" s="24" t="inlineStr">
@@ -4438,7 +4454,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-08-06T19:00:13.149018Z</t>
+          <t>2026-08-10T16:36:36.768051Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4448,22 +4464,22 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>117</v>
+        <v>-178</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>2.17</v>
+        <v>1.561798</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.640288</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
       <c r="BP11" s="25" t="n"/>
       <c r="BQ11" s="27" t="n">
-        <v>2.17</v>
+        <v>1.561798</v>
       </c>
       <c r="BR11" s="28" t="n">
-        <v>0.46</v>
+        <v>0.64</v>
       </c>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
@@ -4500,22 +4516,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>ccd5f17eb0c54739</t>
+          <t>ad7e3212cc9a4377</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T09:11:28.912966Z</t>
+          <t>2026-08-10T16:36:45.039622Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T11:00:00Z</t>
+          <t>2026-08-11T10:00:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>71752</t>
+          <t>77309</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4525,12 +4541,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>FULL SENSE</t>
+          <t>Dragon Ranger Gaming</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Trace Esports</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4550,26 +4566,26 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-156</v>
+        <v>156</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.641026</v>
+        <v>2.56</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.390625</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.781485</v>
+        <v>0.521278</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.17211</v>
+        <v>0.130653</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
@@ -4593,26 +4609,20 @@
         <v>1</v>
       </c>
       <c r="Y12" s="25" t="n"/>
-      <c r="Z12" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="AA12" s="28" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="AB12" s="28" t="n">
-        <v>0.000625</v>
-      </c>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
       <c r="AC12" s="30" t="n">
-        <v>1.2821</v>
+        <v>1.56</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:20:06.633818Z</t>
+          <t>2026-08-11T16:30:37.306342Z</t>
         </is>
       </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-valorant-geng-fs-2026-08-07).</t>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-te-drg-2026-08-11).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4653,32 +4663,32 @@
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>FULL SENSE</t>
+          <t>Dragon Ranger Gaming</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>FULL SENSE</t>
+          <t>Dragon Ranger Gaming</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>FULL SENSE</t>
+          <t>Dragon Ranger Gaming</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Trace Esports</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Trace Esports</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>Gen.G Esports</t>
+          <t>Trace Esports</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4696,7 +4706,7 @@
       </c>
       <c r="BA12" s="24" t="inlineStr">
         <is>
-          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
         </is>
       </c>
       <c r="BB12" s="24" t="inlineStr">
@@ -4711,7 +4721,7 @@
       </c>
       <c r="BD12" s="24" t="inlineStr">
         <is>
-          <t>42b19475ad40d4c6f417c5f7897f490415fd91fcca876fa2415c941da1fd3bc7</t>
+          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
         </is>
       </c>
       <c r="BE12" s="24" t="inlineStr">
@@ -4731,7 +4741,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T09:11:21.351080Z</t>
+          <t>2026-08-10T16:36:39.099981Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4741,23 +4751,19 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-156</v>
+        <v>156</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.641026</v>
+        <v>2.56</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.390625</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
       <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="BR12" s="28" t="n">
-        <v>0.61</v>
-      </c>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
       <c r="BU12" s="25" t="n"/>
@@ -4793,22 +4799,22 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>94a64e146f5740da</t>
+          <t>cf3f1e94a7fd4909</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:24:00.757019Z</t>
+          <t>2026-08-12T14:37:16.864247Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T18:00:00Z</t>
+          <t>2026-08-12T15:00:00Z</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>72078</t>
+          <t>76905</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -4818,12 +4824,12 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>Enterprise Esports</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>Fnatic</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -4833,7 +4839,7 @@
       </c>
       <c r="I13" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J13" s="25" t="n"/>
@@ -4843,26 +4849,26 @@
         </is>
       </c>
       <c r="L13" s="26" t="n">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>2.78</v>
+        <v>3.23</v>
       </c>
       <c r="N13" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.309598</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.743264</v>
+        <v>0.601267</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.383552</v>
+        <v>0.291669</v>
       </c>
       <c r="R13" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S13" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T13" s="24" t="inlineStr">
         <is>
@@ -4880,32 +4886,32 @@
         </is>
       </c>
       <c r="W13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="26" t="n">
         <v>1</v>
-      </c>
-      <c r="X13" s="26" t="n">
-        <v>0</v>
       </c>
       <c r="Y13" s="25" t="n"/>
       <c r="Z13" s="26" t="n">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="AA13" s="28" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="AB13" s="28" t="n">
-        <v>0.000288</v>
+        <v>0.000402</v>
       </c>
       <c r="AC13" s="30" t="n">
-        <v>3.56</v>
+        <v>2.7875</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T21:55:39.052370Z</t>
+          <t>2026-08-12T17:41:06.337138Z</t>
         </is>
       </c>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-valorant-fnc-ep-2026-08-07).</t>
+          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-valorant-sge-gm-2026-08-12).</t>
         </is>
       </c>
       <c r="AF13" s="31" t="inlineStr">
@@ -4946,32 +4952,32 @@
       </c>
       <c r="AP13" s="24" t="inlineStr">
         <is>
-          <t>Enterprise Esports</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="AQ13" s="24" t="inlineStr">
         <is>
-          <t>Enterprise Esports</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="AR13" s="24" t="inlineStr">
         <is>
-          <t>Enterprise Esports</t>
+          <t>Gentle Mates</t>
         </is>
       </c>
       <c r="AS13" s="24" t="inlineStr">
         <is>
-          <t>Fnatic</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AT13" s="24" t="inlineStr">
         <is>
-          <t>Fnatic</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AU13" s="24" t="inlineStr">
         <is>
-          <t>Fnatic</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AV13" s="24" t="n"/>
@@ -4989,7 +4995,7 @@
       </c>
       <c r="BA13" s="24" t="inlineStr">
         <is>
-          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+          <t>544d1cd34df6c8d22913af55b6e1b019f8a76a060474a2450daa185b339b6d8d</t>
         </is>
       </c>
       <c r="BB13" s="24" t="inlineStr">
@@ -5004,7 +5010,7 @@
       </c>
       <c r="BD13" s="24" t="inlineStr">
         <is>
-          <t>81f6739aa819ab85b1d04cc8b0c18852e0f247d6e491c0f3ef1b501fc8699698</t>
+          <t>544d1cd34df6c8d22913af55b6e1b019f8a76a060474a2450daa185b339b6d8d</t>
         </is>
       </c>
       <c r="BE13" s="24" t="inlineStr">
@@ -5024,7 +5030,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-08-07T15:23:54.113763Z</t>
+          <t>2026-08-12T14:37:09.887094Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -5034,22 +5040,22 @@
       </c>
       <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="BL13" s="27" t="n">
-        <v>2.78</v>
+        <v>3.23</v>
       </c>
       <c r="BM13" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.309598</v>
       </c>
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
       <c r="BP13" s="25" t="n"/>
       <c r="BQ13" s="27" t="n">
-        <v>2.78</v>
+        <v>3.23</v>
       </c>
       <c r="BR13" s="28" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
@@ -5086,22 +5092,22 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>e501297caddc4e51</t>
+          <t>57e3e8d6743c492f</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-09T17:08:20.055519Z</t>
+          <t>2026-08-12T17:44:36.247336Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-09T18:00:00Z</t>
+          <t>2026-08-12T18:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>74609</t>
+          <t>76535</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -5111,12 +5117,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>Enterprise Esports</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -5126,7 +5132,7 @@
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J14" s="25" t="n"/>
@@ -5136,26 +5142,26 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>150</v>
+        <v>-138</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>2.5</v>
+        <v>1.724638</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.4</v>
+        <v>0.579832</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.804725</v>
+        <v>0.642814</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.404725</v>
+        <v>0.062982</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
@@ -5173,32 +5179,32 @@
         </is>
       </c>
       <c r="W14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="26" t="n">
         <v>1</v>
-      </c>
-      <c r="X14" s="26" t="n">
-        <v>0</v>
       </c>
       <c r="Y14" s="25" t="n"/>
       <c r="Z14" s="26" t="n">
-        <v>150</v>
+        <v>-138</v>
       </c>
       <c r="AA14" s="28" t="n">
-        <v>0.4</v>
+        <v>0.58</v>
       </c>
       <c r="AB14" s="28" t="n">
-        <v>0</v>
+        <v>0.000168</v>
       </c>
       <c r="AC14" s="30" t="n">
-        <v>3</v>
+        <v>1.087</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-09T20:26:25.086079Z</t>
+          <t>2026-08-12T21:16:01.922323Z</t>
         </is>
       </c>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-valorant-gm-ep-2026-08-09).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-valorant-th-navi-2026-08-12).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -5239,32 +5245,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>Enterprise Esports</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>Enterprise Esports</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>Enterprise Esports</t>
+          <t>Natus Vincere</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -5282,7 +5288,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>43316dd49e7f9b1a20757c6d2b94b720f27a77b2c5fd90af5fff6a8c8dacabc4</t>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -5297,7 +5303,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>43316dd49e7f9b1a20757c6d2b94b720f27a77b2c5fd90af5fff6a8c8dacabc4</t>
+          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5317,7 +5323,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-08-09T17:08:10.558137Z</t>
+          <t>2026-08-12T17:44:26.441713Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5327,22 +5333,22 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>150</v>
+        <v>-138</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>2.5</v>
+        <v>1.724638</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.4</v>
+        <v>0.579832</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
       <c r="BP14" s="25" t="n"/>
       <c r="BQ14" s="27" t="n">
-        <v>2.5</v>
+        <v>1.724638</v>
       </c>
       <c r="BR14" s="28" t="n">
-        <v>0.4</v>
+        <v>0.58</v>
       </c>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
@@ -5379,22 +5385,22 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>7ab28900c23e400a</t>
+          <t>f12c407eb5fa422e</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-10T16:36:45.039622Z</t>
+          <t>2026-08-12T21:33:44.211826Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-10T22:00:00Z</t>
+          <t>2026-08-12T23:30:00Z</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>75255</t>
+          <t>78205</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -5404,12 +5410,12 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>Olimpo Gold</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>NPC Team</t>
+          <t>MVSK Secret</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5419,7 +5425,7 @@
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J15" s="25" t="n"/>
@@ -5429,20 +5435,20 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>2.5</v>
+        <v>3.03</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.4</v>
+        <v>0.330033</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.559409</v>
+        <v>0.519894</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>0.159409</v>
+        <v>0.189861</v>
       </c>
       <c r="R15" s="26" t="n">
         <v>100</v>
@@ -5466,32 +5472,32 @@
         </is>
       </c>
       <c r="W15" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" s="26" t="n">
         <v>0</v>
-      </c>
-      <c r="X15" s="26" t="n">
-        <v>1</v>
       </c>
       <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="AA15" s="28" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AB15" s="28" t="n">
-        <v>0</v>
+        <v>-3.3e-05</v>
       </c>
       <c r="AC15" s="30" t="n">
         <v>-1</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-11T13:09:08.912134Z</t>
+          <t>2026-08-13T05:35:04.870447Z</t>
         </is>
       </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-valorant-ntp-og-2026-08-10).</t>
+          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-valorant-mvs-spi-2026-08-12).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5532,32 +5538,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>Olimpo Gold</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>Olimpo Gold</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>Olimpo Gold</t>
+          <t>The Spiders</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>NPC Team</t>
+          <t>MVSK Secret</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>NPC Team</t>
+          <t>MVSK Secret</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>NPC Team</t>
+          <t>MVSK Secret</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5575,7 +5581,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
+          <t>b58416f26420ee9d55d05ce1518c442566f4b73f4e41b9531abbe4559267bbea</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5590,7 +5596,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
+          <t>b58416f26420ee9d55d05ce1518c442566f4b73f4e41b9531abbe4559267bbea</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5610,7 +5616,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-08-10T16:36:32.706040Z</t>
+          <t>2026-08-12T21:33:38.241347Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5620,22 +5626,22 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>2.5</v>
+        <v>3.03</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.4</v>
+        <v>0.330033</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
       <c r="BP15" s="25" t="n"/>
       <c r="BQ15" s="27" t="n">
-        <v>2.5</v>
+        <v>3.03</v>
       </c>
       <c r="BR15" s="28" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
@@ -5672,22 +5678,22 @@
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>eb53910bc62343f1</t>
+          <t>ac40560f7d5149c4</t>
         </is>
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-10T16:36:45.039622Z</t>
+          <t>2026-08-12T21:33:44.211826Z</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-11T01:00:00Z</t>
+          <t>2026-08-14T00:00:00Z</t>
         </is>
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>75257</t>
+          <t>78063</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
@@ -5697,12 +5703,12 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>FUSION X</t>
+          <t>M80</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>MYVRA GC</t>
+          <t>Team Envy</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
@@ -5712,7 +5718,7 @@
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J16" s="25" t="n"/>
@@ -5722,23 +5728,23 @@
         </is>
       </c>
       <c r="L16" s="26" t="n">
-        <v>-178</v>
+        <v>-144</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.694444</v>
       </c>
       <c r="N16" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.590164</v>
       </c>
       <c r="O16" s="28" t="n">
-        <v>0.750891</v>
+        <v>0.7639010000000001</v>
       </c>
       <c r="P16" s="28" t="n"/>
       <c r="Q16" s="28" t="n">
-        <v>0.110603</v>
+        <v>0.173737</v>
       </c>
       <c r="R16" s="26" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="S16" s="29" t="n">
         <v>2</v>
@@ -5764,7 +5770,7 @@
       <c r="AD16" s="24" t="n"/>
       <c r="AE16" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-valorant-myvgc-fsnx-2026-08-11).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-valorant-nv-m80-2026-08-14).</t>
         </is>
       </c>
       <c r="AF16" s="31" t="inlineStr">
@@ -5805,32 +5811,32 @@
       </c>
       <c r="AP16" s="24" t="inlineStr">
         <is>
-          <t>FUSION X</t>
+          <t>M80</t>
         </is>
       </c>
       <c r="AQ16" s="24" t="inlineStr">
         <is>
-          <t>FUSION X</t>
+          <t>M80</t>
         </is>
       </c>
       <c r="AR16" s="24" t="inlineStr">
         <is>
-          <t>FUSION X</t>
+          <t>M80</t>
         </is>
       </c>
       <c r="AS16" s="24" t="inlineStr">
         <is>
-          <t>MYVRA GC</t>
+          <t>Team Envy</t>
         </is>
       </c>
       <c r="AT16" s="24" t="inlineStr">
         <is>
-          <t>MYVRA GC</t>
+          <t>Team Envy</t>
         </is>
       </c>
       <c r="AU16" s="24" t="inlineStr">
         <is>
-          <t>MYVRA GC</t>
+          <t>Team Envy</t>
         </is>
       </c>
       <c r="AV16" s="24" t="n"/>
@@ -5848,7 +5854,7 @@
       </c>
       <c r="BA16" s="24" t="inlineStr">
         <is>
-          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
+          <t>b58416f26420ee9d55d05ce1518c442566f4b73f4e41b9531abbe4559267bbea</t>
         </is>
       </c>
       <c r="BB16" s="24" t="inlineStr">
@@ -5863,7 +5869,7 @@
       </c>
       <c r="BD16" s="24" t="inlineStr">
         <is>
-          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
+          <t>b58416f26420ee9d55d05ce1518c442566f4b73f4e41b9531abbe4559267bbea</t>
         </is>
       </c>
       <c r="BE16" s="24" t="inlineStr">
@@ -5883,7 +5889,7 @@
       </c>
       <c r="BH16" s="24" t="inlineStr">
         <is>
-          <t>2026-08-10T16:36:36.768051Z</t>
+          <t>2026-08-12T21:33:44.207376Z</t>
         </is>
       </c>
       <c r="BI16" s="24" t="inlineStr">
@@ -5893,13 +5899,13 @@
       </c>
       <c r="BJ16" s="25" t="n"/>
       <c r="BK16" s="26" t="n">
-        <v>-178</v>
+        <v>-144</v>
       </c>
       <c r="BL16" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.694444</v>
       </c>
       <c r="BM16" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.590164</v>
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
@@ -5941,22 +5947,22 @@
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>ad7e3212cc9a4377</t>
+          <t>04690384ff704ac0</t>
         </is>
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-10T16:36:45.039622Z</t>
+          <t>2026-08-13T07:33:38.167763Z</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-11T10:00:00Z</t>
+          <t>2026-08-13T08:00:00Z</t>
         </is>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>77309</t>
+          <t>77171</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
@@ -5966,12 +5972,12 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>Dragon Ranger Gaming</t>
+          <t>ONSIDE GAMING</t>
         </is>
       </c>
       <c r="G17" s="24" t="inlineStr">
         <is>
-          <t>Trace Esports</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="H17" s="24" t="inlineStr">
@@ -5981,7 +5987,7 @@
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J17" s="25" t="n"/>
@@ -5991,26 +5997,26 @@
         </is>
       </c>
       <c r="L17" s="26" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="N17" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.45045</v>
       </c>
       <c r="O17" s="28" t="n">
-        <v>0.521278</v>
+        <v>0.577877</v>
       </c>
       <c r="P17" s="28" t="n"/>
       <c r="Q17" s="28" t="n">
-        <v>0.130653</v>
+        <v>0.127427</v>
       </c>
       <c r="R17" s="26" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
@@ -6024,7 +6030,7 @@
       </c>
       <c r="V17" s="24" t="inlineStr">
         <is>
-          <t>win</t>
+          <t>loss</t>
         </is>
       </c>
       <c r="W17" s="26" t="n">
@@ -6034,20 +6040,26 @@
         <v>1</v>
       </c>
       <c r="Y17" s="25" t="n"/>
-      <c r="Z17" s="26" t="n"/>
-      <c r="AA17" s="28" t="n"/>
-      <c r="AB17" s="28" t="n"/>
+      <c r="Z17" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA17" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB17" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
       <c r="AC17" s="30" t="n">
-        <v>1.56</v>
+        <v>-1.25</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-11T16:30:37.306342Z</t>
+          <t>2026-08-13T10:07:19.927616Z</t>
         </is>
       </c>
       <c r="AE17" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-valorant-te-drg-2026-08-11).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-valorant-krx-osg-2026-08-13).</t>
         </is>
       </c>
       <c r="AF17" s="31" t="inlineStr">
@@ -6057,7 +6069,7 @@
       </c>
       <c r="AG17" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH17" s="24" t="n"/>
@@ -6088,32 +6100,32 @@
       </c>
       <c r="AP17" s="24" t="inlineStr">
         <is>
-          <t>Dragon Ranger Gaming</t>
+          <t>ONSIDE GAMING</t>
         </is>
       </c>
       <c r="AQ17" s="24" t="inlineStr">
         <is>
-          <t>Dragon Ranger Gaming</t>
+          <t>ONSIDE GAMING</t>
         </is>
       </c>
       <c r="AR17" s="24" t="inlineStr">
         <is>
-          <t>Dragon Ranger Gaming</t>
+          <t>ONSIDE GAMING</t>
         </is>
       </c>
       <c r="AS17" s="24" t="inlineStr">
         <is>
-          <t>Trace Esports</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AT17" s="24" t="inlineStr">
         <is>
-          <t>Trace Esports</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AU17" s="24" t="inlineStr">
         <is>
-          <t>Trace Esports</t>
+          <t>Kiwoom DRX</t>
         </is>
       </c>
       <c r="AV17" s="24" t="n"/>
@@ -6131,7 +6143,7 @@
       </c>
       <c r="BA17" s="24" t="inlineStr">
         <is>
-          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
+          <t>9a4dfa85f36adcfca5ea0511c0f369e0181e4aa5804896696079fbe36b54d3d2</t>
         </is>
       </c>
       <c r="BB17" s="24" t="inlineStr">
@@ -6146,7 +6158,7 @@
       </c>
       <c r="BD17" s="24" t="inlineStr">
         <is>
-          <t>2bc5ea39dc27eb41c7f3cbd9b58da9bee3940cd90f1ffefbd7b6a82f96fdee45</t>
+          <t>9a4dfa85f36adcfca5ea0511c0f369e0181e4aa5804896696079fbe36b54d3d2</t>
         </is>
       </c>
       <c r="BE17" s="24" t="inlineStr">
@@ -6166,7 +6178,7 @@
       </c>
       <c r="BH17" s="24" t="inlineStr">
         <is>
-          <t>2026-08-10T16:36:39.099981Z</t>
+          <t>2026-08-13T07:33:28.262454Z</t>
         </is>
       </c>
       <c r="BI17" s="24" t="inlineStr">
@@ -6176,19 +6188,23 @@
       </c>
       <c r="BJ17" s="25" t="n"/>
       <c r="BK17" s="26" t="n">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="BL17" s="27" t="n">
-        <v>2.56</v>
+        <v>2.22</v>
       </c>
       <c r="BM17" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.45045</v>
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
       <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
-      <c r="BR17" s="28" t="n"/>
+      <c r="BQ17" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR17" s="28" t="n">
+        <v>0.45</v>
+      </c>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
       <c r="BU17" s="25" t="n"/>
@@ -6224,22 +6240,22 @@
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>cf3f1e94a7fd4909</t>
+          <t>1482f36956e24813</t>
         </is>
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T14:37:16.864247Z</t>
+          <t>2026-08-13T10:40:22.988810Z</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T15:00:00Z</t>
+          <t>2026-08-13T11:00:00Z</t>
         </is>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>76905</t>
+          <t>77227</t>
         </is>
       </c>
       <c r="E18" s="24" t="inlineStr">
@@ -6249,12 +6265,12 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Sharper Esport</t>
         </is>
       </c>
       <c r="G18" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Rex Regum Qeon</t>
         </is>
       </c>
       <c r="H18" s="24" t="inlineStr">
@@ -6264,7 +6280,7 @@
       </c>
       <c r="I18" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J18" s="25" t="n"/>
@@ -6274,26 +6290,26 @@
         </is>
       </c>
       <c r="L18" s="26" t="n">
-        <v>223</v>
+        <v>178</v>
       </c>
       <c r="M18" s="27" t="n">
-        <v>3.23</v>
+        <v>2.78</v>
       </c>
       <c r="N18" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.359712</v>
       </c>
       <c r="O18" s="28" t="n">
-        <v>0.601267</v>
+        <v>0.5357769999999999</v>
       </c>
       <c r="P18" s="28" t="n"/>
       <c r="Q18" s="28" t="n">
-        <v>0.291669</v>
+        <v>0.176065</v>
       </c>
       <c r="R18" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T18" s="24" t="inlineStr">
         <is>
@@ -6311,32 +6327,32 @@
         </is>
       </c>
       <c r="W18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="26" t="n">
         <v>0</v>
-      </c>
-      <c r="X18" s="26" t="n">
-        <v>1</v>
       </c>
       <c r="Y18" s="25" t="n"/>
       <c r="Z18" s="26" t="n">
-        <v>223</v>
+        <v>113</v>
       </c>
       <c r="AA18" s="28" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="AB18" s="28" t="n">
-        <v>0.000402</v>
+        <v>0.110288</v>
       </c>
       <c r="AC18" s="30" t="n">
-        <v>2.7875</v>
+        <v>1.78</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:41:06.337138Z</t>
+          <t>2026-08-13T13:43:46.349925Z</t>
         </is>
       </c>
       <c r="AE18" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-valorant-sge-gm-2026-08-12).</t>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-valorant-rrq-spe-2026-08-13).</t>
         </is>
       </c>
       <c r="AF18" s="31" t="inlineStr">
@@ -6377,32 +6393,32 @@
       </c>
       <c r="AP18" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Sharper Esport</t>
         </is>
       </c>
       <c r="AQ18" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Sharper Esport</t>
         </is>
       </c>
       <c r="AR18" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates</t>
+          <t>Sharper Esport</t>
         </is>
       </c>
       <c r="AS18" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Rex Regum Qeon</t>
         </is>
       </c>
       <c r="AT18" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Rex Regum Qeon</t>
         </is>
       </c>
       <c r="AU18" s="24" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Rex Regum Qeon</t>
         </is>
       </c>
       <c r="AV18" s="24" t="n"/>
@@ -6420,7 +6436,7 @@
       </c>
       <c r="BA18" s="24" t="inlineStr">
         <is>
-          <t>544d1cd34df6c8d22913af55b6e1b019f8a76a060474a2450daa185b339b6d8d</t>
+          <t>34c63be26d0e2cc14119f679adaf024aa89287fce612ad18898d49f1dee15418</t>
         </is>
       </c>
       <c r="BB18" s="24" t="inlineStr">
@@ -6435,7 +6451,7 @@
       </c>
       <c r="BD18" s="24" t="inlineStr">
         <is>
-          <t>544d1cd34df6c8d22913af55b6e1b019f8a76a060474a2450daa185b339b6d8d</t>
+          <t>34c63be26d0e2cc14119f679adaf024aa89287fce612ad18898d49f1dee15418</t>
         </is>
       </c>
       <c r="BE18" s="24" t="inlineStr">
@@ -6455,7 +6471,7 @@
       </c>
       <c r="BH18" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T14:37:09.887094Z</t>
+          <t>2026-08-13T10:40:13.696977Z</t>
         </is>
       </c>
       <c r="BI18" s="24" t="inlineStr">
@@ -6465,22 +6481,22 @@
       </c>
       <c r="BJ18" s="25" t="n"/>
       <c r="BK18" s="26" t="n">
-        <v>223</v>
+        <v>178</v>
       </c>
       <c r="BL18" s="27" t="n">
-        <v>3.23</v>
+        <v>2.78</v>
       </c>
       <c r="BM18" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.359712</v>
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
       <c r="BP18" s="25" t="n"/>
       <c r="BQ18" s="27" t="n">
-        <v>3.23</v>
+        <v>2.13</v>
       </c>
       <c r="BR18" s="28" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
@@ -6517,22 +6533,22 @@
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>57e3e8d6743c492f</t>
+          <t>4f966ce4648f49ec</t>
         </is>
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:36.247336Z</t>
+          <t>2026-08-13T13:47:19.845301Z</t>
         </is>
       </c>
       <c r="C19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T18:00:00Z</t>
+          <t>2026-08-13T15:00:00Z</t>
         </is>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>76535</t>
+          <t>77363</t>
         </is>
       </c>
       <c r="E19" s="24" t="inlineStr">
@@ -6542,12 +6558,12 @@
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Pcific Esports</t>
         </is>
       </c>
       <c r="G19" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="H19" s="24" t="inlineStr">
@@ -6567,26 +6583,26 @@
         </is>
       </c>
       <c r="L19" s="26" t="n">
-        <v>-138</v>
+        <v>-233</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.429185</v>
       </c>
       <c r="N19" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.6997</v>
       </c>
       <c r="O19" s="28" t="n">
-        <v>0.642814</v>
+        <v>0.83509</v>
       </c>
       <c r="P19" s="28" t="n"/>
       <c r="Q19" s="28" t="n">
-        <v>0.062982</v>
+        <v>0.13539</v>
       </c>
       <c r="R19" s="26" t="n">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="S19" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T19" s="24" t="inlineStr">
         <is>
@@ -6609,7 +6625,7 @@
       <c r="AD19" s="24" t="n"/>
       <c r="AE19" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-valorant-th-navi-2026-08-12).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-valorant-jl-pcfic-2026-08-13).</t>
         </is>
       </c>
       <c r="AF19" s="31" t="inlineStr">
@@ -6650,32 +6666,32 @@
       </c>
       <c r="AP19" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Pcific Esports</t>
         </is>
       </c>
       <c r="AQ19" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Pcific Esports</t>
         </is>
       </c>
       <c r="AR19" s="24" t="inlineStr">
         <is>
-          <t>Natus Vincere</t>
+          <t>Pcific Esports</t>
         </is>
       </c>
       <c r="AS19" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AT19" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AU19" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics</t>
+          <t>Joblife</t>
         </is>
       </c>
       <c r="AV19" s="24" t="n"/>
@@ -6693,7 +6709,7 @@
       </c>
       <c r="BA19" s="24" t="inlineStr">
         <is>
-          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+          <t>da0677ab8abe2b527063872e9a3414ee4e73a14497c101342ddcfce29bd189b4</t>
         </is>
       </c>
       <c r="BB19" s="24" t="inlineStr">
@@ -6708,7 +6724,7 @@
       </c>
       <c r="BD19" s="24" t="inlineStr">
         <is>
-          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+          <t>da0677ab8abe2b527063872e9a3414ee4e73a14497c101342ddcfce29bd189b4</t>
         </is>
       </c>
       <c r="BE19" s="24" t="inlineStr">
@@ -6728,7 +6744,7 @@
       </c>
       <c r="BH19" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:26.441713Z</t>
+          <t>2026-08-13T13:47:13.179473Z</t>
         </is>
       </c>
       <c r="BI19" s="24" t="inlineStr">
@@ -6738,13 +6754,13 @@
       </c>
       <c r="BJ19" s="25" t="n"/>
       <c r="BK19" s="26" t="n">
-        <v>-138</v>
+        <v>-233</v>
       </c>
       <c r="BL19" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.429185</v>
       </c>
       <c r="BM19" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.6997</v>
       </c>
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
@@ -6786,22 +6802,22 @@
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>43aa834f71984e7b</t>
+          <t>0728924806414578</t>
         </is>
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:36.247336Z</t>
+          <t>2026-08-13T17:16:26.831639Z</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T23:30:00Z</t>
+          <t>2026-08-13T18:00:00Z</t>
         </is>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>78205</t>
+          <t>77546</t>
         </is>
       </c>
       <c r="E20" s="24" t="inlineStr">
@@ -6811,12 +6827,12 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>Gentle Mates GC</t>
         </is>
       </c>
       <c r="G20" s="24" t="inlineStr">
         <is>
-          <t>MVSK Secret</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="H20" s="24" t="inlineStr">
@@ -6826,7 +6842,7 @@
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J20" s="25" t="n"/>
@@ -6836,26 +6852,26 @@
         </is>
       </c>
       <c r="L20" s="26" t="n">
-        <v>203</v>
+        <v>-144</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>3.03</v>
+        <v>1.694444</v>
       </c>
       <c r="N20" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.590164</v>
       </c>
       <c r="O20" s="28" t="n">
-        <v>0.519891</v>
+        <v>0.687518</v>
       </c>
       <c r="P20" s="28" t="n"/>
       <c r="Q20" s="28" t="n">
-        <v>0.189858</v>
+        <v>0.097354</v>
       </c>
       <c r="R20" s="26" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="S20" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
@@ -6878,7 +6894,7 @@
       <c r="AD20" s="24" t="n"/>
       <c r="AE20" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-valorant-mvs-spi-2026-08-12).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-valorant-fso-m8gc-2026-08-13).</t>
         </is>
       </c>
       <c r="AF20" s="31" t="inlineStr">
@@ -6919,32 +6935,32 @@
       </c>
       <c r="AP20" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>Gentle Mates GC</t>
         </is>
       </c>
       <c r="AQ20" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>Gentle Mates GC</t>
         </is>
       </c>
       <c r="AR20" s="24" t="inlineStr">
         <is>
-          <t>The Spiders</t>
+          <t>Gentle Mates GC</t>
         </is>
       </c>
       <c r="AS20" s="24" t="inlineStr">
         <is>
-          <t>MVSK Secret</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="AT20" s="24" t="inlineStr">
         <is>
-          <t>MVSK Secret</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="AU20" s="24" t="inlineStr">
         <is>
-          <t>MVSK Secret</t>
+          <t>FOKUS Sakura</t>
         </is>
       </c>
       <c r="AV20" s="24" t="n"/>
@@ -6962,7 +6978,7 @@
       </c>
       <c r="BA20" s="24" t="inlineStr">
         <is>
-          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+          <t>b7c1dabbbbc9554691b923884077a0c9e2fdb894454c83cbe181c9fcf1b2e71f</t>
         </is>
       </c>
       <c r="BB20" s="24" t="inlineStr">
@@ -6977,7 +6993,7 @@
       </c>
       <c r="BD20" s="24" t="inlineStr">
         <is>
-          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+          <t>b7c1dabbbbc9554691b923884077a0c9e2fdb894454c83cbe181c9fcf1b2e71f</t>
         </is>
       </c>
       <c r="BE20" s="24" t="inlineStr">
@@ -6997,7 +7013,7 @@
       </c>
       <c r="BH20" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:30.097634Z</t>
+          <t>2026-08-13T17:16:20.850586Z</t>
         </is>
       </c>
       <c r="BI20" s="24" t="inlineStr">
@@ -7007,13 +7023,13 @@
       </c>
       <c r="BJ20" s="25" t="n"/>
       <c r="BK20" s="26" t="n">
-        <v>203</v>
+        <v>-144</v>
       </c>
       <c r="BL20" s="27" t="n">
-        <v>3.03</v>
+        <v>1.694444</v>
       </c>
       <c r="BM20" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.590164</v>
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
@@ -7055,22 +7071,22 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>dbc6d13bad474b15</t>
+          <t>5a4977b0f1a44ade</t>
         </is>
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:36.247336Z</t>
+          <t>2026-08-13T17:16:26.831639Z</t>
         </is>
       </c>
       <c r="C21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-13T08:00:00Z</t>
+          <t>2026-08-13T21:00:00Z</t>
         </is>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>77171</t>
+          <t>77923</t>
         </is>
       </c>
       <c r="E21" s="24" t="inlineStr">
@@ -7080,12 +7096,12 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>ONSIDE GAMING</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="G21" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>KRÜ Esports</t>
         </is>
       </c>
       <c r="H21" s="24" t="inlineStr">
@@ -7105,26 +7121,26 @@
         </is>
       </c>
       <c r="L21" s="26" t="n">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>2.38</v>
+        <v>2.94</v>
       </c>
       <c r="N21" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.340136</v>
       </c>
       <c r="O21" s="28" t="n">
-        <v>0.578341</v>
+        <v>0.725256</v>
       </c>
       <c r="P21" s="28" t="n"/>
       <c r="Q21" s="28" t="n">
-        <v>0.158173</v>
+        <v>0.38512</v>
       </c>
       <c r="R21" s="26" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
@@ -7147,7 +7163,7 @@
       <c r="AD21" s="24" t="n"/>
       <c r="AE21" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-valorant-krx-osg-2026-08-13).</t>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-valorant-kr-bst-2026-08-13).</t>
         </is>
       </c>
       <c r="AF21" s="31" t="inlineStr">
@@ -7188,32 +7204,32 @@
       </c>
       <c r="AP21" s="24" t="inlineStr">
         <is>
-          <t>ONSIDE GAMING</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AQ21" s="24" t="inlineStr">
         <is>
-          <t>ONSIDE GAMING</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AR21" s="24" t="inlineStr">
         <is>
-          <t>ONSIDE GAMING</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AS21" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>KRÜ Esports</t>
         </is>
       </c>
       <c r="AT21" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>KRÜ Esports</t>
         </is>
       </c>
       <c r="AU21" s="24" t="inlineStr">
         <is>
-          <t>Kiwoom DRX</t>
+          <t>KRÜ Esports</t>
         </is>
       </c>
       <c r="AV21" s="24" t="n"/>
@@ -7231,7 +7247,7 @@
       </c>
       <c r="BA21" s="24" t="inlineStr">
         <is>
-          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+          <t>b7c1dabbbbc9554691b923884077a0c9e2fdb894454c83cbe181c9fcf1b2e71f</t>
         </is>
       </c>
       <c r="BB21" s="24" t="inlineStr">
@@ -7246,7 +7262,7 @@
       </c>
       <c r="BD21" s="24" t="inlineStr">
         <is>
-          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+          <t>b7c1dabbbbc9554691b923884077a0c9e2fdb894454c83cbe181c9fcf1b2e71f</t>
         </is>
       </c>
       <c r="BE21" s="24" t="inlineStr">
@@ -7266,7 +7282,7 @@
       </c>
       <c r="BH21" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:30.751879Z</t>
+          <t>2026-08-13T17:16:21.352013Z</t>
         </is>
       </c>
       <c r="BI21" s="24" t="inlineStr">
@@ -7276,13 +7292,13 @@
       </c>
       <c r="BJ21" s="25" t="n"/>
       <c r="BK21" s="26" t="n">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="BL21" s="27" t="n">
-        <v>2.38</v>
+        <v>2.94</v>
       </c>
       <c r="BM21" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.340136</v>
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
@@ -7324,22 +7340,22 @@
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>9d4ef0378675480d</t>
+          <t>4e2ae7512bc840db</t>
         </is>
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:36.247336Z</t>
+          <t>2026-08-13T17:16:26.831639Z</t>
         </is>
       </c>
       <c r="C22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-13T11:00:00Z</t>
+          <t>2026-08-14T08:00:00Z</t>
         </is>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>77227</t>
+          <t>79716</t>
         </is>
       </c>
       <c r="E22" s="24" t="inlineStr">
@@ -7349,12 +7365,12 @@
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>Sharper Esport</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="G22" s="24" t="inlineStr">
         <is>
-          <t>Rex Regum Qeon</t>
+          <t>Nova Esports</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -7364,7 +7380,7 @@
       </c>
       <c r="I22" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J22" s="25" t="n"/>
@@ -7374,26 +7390,26 @@
         </is>
       </c>
       <c r="L22" s="26" t="n">
-        <v>212</v>
+        <v>-194</v>
       </c>
       <c r="M22" s="27" t="n">
-        <v>3.12</v>
+        <v>1.515464</v>
       </c>
       <c r="N22" s="28" t="n">
-        <v>0.320513</v>
+        <v>0.659864</v>
       </c>
       <c r="O22" s="28" t="n">
-        <v>0.536314</v>
+        <v>0.796037</v>
       </c>
       <c r="P22" s="28" t="n"/>
       <c r="Q22" s="28" t="n">
-        <v>0.215801</v>
+        <v>0.136173</v>
       </c>
       <c r="R22" s="26" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="S22" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T22" s="24" t="inlineStr">
         <is>
@@ -7416,7 +7432,7 @@
       <c r="AD22" s="24" t="n"/>
       <c r="AE22" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3200 (market_slug=aec-valorant-rrq-spe-2026-08-13).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-nova-jdg-2026-08-14).</t>
         </is>
       </c>
       <c r="AF22" s="31" t="inlineStr">
@@ -7457,32 +7473,32 @@
       </c>
       <c r="AP22" s="24" t="inlineStr">
         <is>
-          <t>Sharper Esport</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AQ22" s="24" t="inlineStr">
         <is>
-          <t>Sharper Esport</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AR22" s="24" t="inlineStr">
         <is>
-          <t>Sharper Esport</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AS22" s="24" t="inlineStr">
         <is>
-          <t>Rex Regum Qeon</t>
+          <t>Nova Esports</t>
         </is>
       </c>
       <c r="AT22" s="24" t="inlineStr">
         <is>
-          <t>Rex Regum Qeon</t>
+          <t>Nova Esports</t>
         </is>
       </c>
       <c r="AU22" s="24" t="inlineStr">
         <is>
-          <t>Rex Regum Qeon</t>
+          <t>Nova Esports</t>
         </is>
       </c>
       <c r="AV22" s="24" t="n"/>
@@ -7500,7 +7516,7 @@
       </c>
       <c r="BA22" s="24" t="inlineStr">
         <is>
-          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+          <t>b7c1dabbbbc9554691b923884077a0c9e2fdb894454c83cbe181c9fcf1b2e71f</t>
         </is>
       </c>
       <c r="BB22" s="24" t="inlineStr">
@@ -7515,7 +7531,7 @@
       </c>
       <c r="BD22" s="24" t="inlineStr">
         <is>
-          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+          <t>b7c1dabbbbc9554691b923884077a0c9e2fdb894454c83cbe181c9fcf1b2e71f</t>
         </is>
       </c>
       <c r="BE22" s="24" t="inlineStr">
@@ -7535,7 +7551,7 @@
       </c>
       <c r="BH22" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:31.632005Z</t>
+          <t>2026-08-13T17:16:22.475350Z</t>
         </is>
       </c>
       <c r="BI22" s="24" t="inlineStr">
@@ -7545,13 +7561,13 @@
       </c>
       <c r="BJ22" s="25" t="n"/>
       <c r="BK22" s="26" t="n">
-        <v>212</v>
+        <v>-194</v>
       </c>
       <c r="BL22" s="27" t="n">
-        <v>3.12</v>
+        <v>1.515464</v>
       </c>
       <c r="BM22" s="28" t="n">
-        <v>0.320513</v>
+        <v>0.659864</v>
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
@@ -7593,22 +7609,22 @@
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>33afde8b41694dbd</t>
+          <t>c7fbd9d15a1b48df</t>
         </is>
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:36.247336Z</t>
+          <t>2026-08-13T17:16:26.831639Z</t>
         </is>
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-13T18:00:00Z</t>
+          <t>2026-08-14T11:00:00Z</t>
         </is>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>77546</t>
+          <t>78288</t>
         </is>
       </c>
       <c r="E23" s="24" t="inlineStr">
@@ -7618,12 +7634,12 @@
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates GC</t>
+          <t>Xipto Esports</t>
         </is>
       </c>
       <c r="G23" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>Team Secret</t>
         </is>
       </c>
       <c r="H23" s="24" t="inlineStr">
@@ -7643,26 +7659,26 @@
         </is>
       </c>
       <c r="L23" s="26" t="n">
-        <v>-194</v>
+        <v>108</v>
       </c>
       <c r="M23" s="27" t="n">
-        <v>1.515464</v>
+        <v>2.08</v>
       </c>
       <c r="N23" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.480769</v>
       </c>
       <c r="O23" s="28" t="n">
-        <v>0.689042</v>
+        <v>0.53228</v>
       </c>
       <c r="P23" s="28" t="n"/>
       <c r="Q23" s="28" t="n">
-        <v>0.029178</v>
+        <v>0.051511</v>
       </c>
       <c r="R23" s="26" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="S23" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T23" s="24" t="inlineStr">
         <is>
@@ -7685,7 +7701,7 @@
       <c r="AD23" s="24" t="n"/>
       <c r="AE23" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-valorant-fso-m8gc-2026-08-13).</t>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-valorant-ts-xe-2026-08-14).</t>
         </is>
       </c>
       <c r="AF23" s="31" t="inlineStr">
@@ -7726,32 +7742,32 @@
       </c>
       <c r="AP23" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates GC</t>
+          <t>Xipto Esports</t>
         </is>
       </c>
       <c r="AQ23" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates GC</t>
+          <t>Xipto Esports</t>
         </is>
       </c>
       <c r="AR23" s="24" t="inlineStr">
         <is>
-          <t>Gentle Mates GC</t>
+          <t>Xipto Esports</t>
         </is>
       </c>
       <c r="AS23" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>Team Secret</t>
         </is>
       </c>
       <c r="AT23" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>Team Secret</t>
         </is>
       </c>
       <c r="AU23" s="24" t="inlineStr">
         <is>
-          <t>FOKUS Sakura</t>
+          <t>Team Secret</t>
         </is>
       </c>
       <c r="AV23" s="24" t="n"/>
@@ -7769,7 +7785,7 @@
       </c>
       <c r="BA23" s="24" t="inlineStr">
         <is>
-          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+          <t>b7c1dabbbbc9554691b923884077a0c9e2fdb894454c83cbe181c9fcf1b2e71f</t>
         </is>
       </c>
       <c r="BB23" s="24" t="inlineStr">
@@ -7784,7 +7800,7 @@
       </c>
       <c r="BD23" s="24" t="inlineStr">
         <is>
-          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+          <t>b7c1dabbbbc9554691b923884077a0c9e2fdb894454c83cbe181c9fcf1b2e71f</t>
         </is>
       </c>
       <c r="BE23" s="24" t="inlineStr">
@@ -7804,7 +7820,7 @@
       </c>
       <c r="BH23" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:34.768410Z</t>
+          <t>2026-08-13T17:16:24.113436Z</t>
         </is>
       </c>
       <c r="BI23" s="24" t="inlineStr">
@@ -7814,13 +7830,13 @@
       </c>
       <c r="BJ23" s="25" t="n"/>
       <c r="BK23" s="26" t="n">
-        <v>-194</v>
+        <v>108</v>
       </c>
       <c r="BL23" s="27" t="n">
-        <v>1.515464</v>
+        <v>2.08</v>
       </c>
       <c r="BM23" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.480769</v>
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
@@ -7862,22 +7878,22 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>056633cd5d054196</t>
+          <t>98147a0ef22f45c3</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:36.247336Z</t>
+          <t>2026-08-13T17:16:26.831639Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-13T21:00:00Z</t>
+          <t>2026-08-14T15:00:00Z</t>
         </is>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>77923</t>
+          <t>80237</t>
         </is>
       </c>
       <c r="E24" s="24" t="inlineStr">
@@ -7887,12 +7903,12 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="G24" s="24" t="inlineStr">
         <is>
-          <t>KRÜ Esports</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -7902,7 +7918,7 @@
       </c>
       <c r="I24" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J24" s="25" t="n"/>
@@ -7912,26 +7928,26 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.4</v>
+        <v>0.340136</v>
       </c>
       <c r="O24" s="28" t="n">
-        <v>0.727042</v>
+        <v>0.57906</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>0.327042</v>
+        <v>0.238924</v>
       </c>
       <c r="R24" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S24" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T24" s="24" t="inlineStr">
         <is>
@@ -7954,7 +7970,7 @@
       <c r="AD24" s="24" t="n"/>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-valorant-kr-bst-2026-08-13).</t>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-valorant-sge-th-2026-08-14).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -7995,32 +8011,32 @@
       </c>
       <c r="AP24" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AQ24" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AR24" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>Team Heretics</t>
         </is>
       </c>
       <c r="AS24" s="24" t="inlineStr">
         <is>
-          <t>KRÜ Esports</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AT24" s="24" t="inlineStr">
         <is>
-          <t>KRÜ Esports</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AU24" s="24" t="inlineStr">
         <is>
-          <t>KRÜ Esports</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="AV24" s="24" t="n"/>
@@ -8038,7 +8054,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+          <t>b7c1dabbbbc9554691b923884077a0c9e2fdb894454c83cbe181c9fcf1b2e71f</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -8053,7 +8069,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+          <t>b7c1dabbbbc9554691b923884077a0c9e2fdb894454c83cbe181c9fcf1b2e71f</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -8073,7 +8089,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:35.503645Z</t>
+          <t>2026-08-13T17:16:25.175831Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -8083,13 +8099,13 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>2.5</v>
+        <v>2.94</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.4</v>
+        <v>0.340136</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
@@ -8131,22 +8147,22 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>19436ce53cdb4af4</t>
+          <t>12c6ec5c808845af</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:36.247336Z</t>
+          <t>2026-08-13T17:16:26.831639Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-14T00:00:00Z</t>
+          <t>2026-08-14T18:00:00Z</t>
         </is>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>78063</t>
+          <t>78828</t>
         </is>
       </c>
       <c r="E25" s="24" t="inlineStr">
@@ -8156,12 +8172,12 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>M80</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="G25" s="24" t="inlineStr">
         <is>
-          <t>Team Envy</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -8171,7 +8187,7 @@
       </c>
       <c r="I25" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J25" s="25" t="n"/>
@@ -8181,26 +8197,26 @@
         </is>
       </c>
       <c r="L25" s="26" t="n">
-        <v>-144</v>
+        <v>113</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.13</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.469484</v>
       </c>
       <c r="O25" s="28" t="n">
-        <v>0.764164</v>
+        <v>0.541928</v>
       </c>
       <c r="P25" s="28" t="n"/>
       <c r="Q25" s="28" t="n">
-        <v>0.174</v>
+        <v>0.07244399999999999</v>
       </c>
       <c r="R25" s="26" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
@@ -8223,7 +8239,7 @@
       <c r="AD25" s="24" t="n"/>
       <c r="AE25" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-valorant-nv-m80-2026-08-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-valorant-tmo-skn-2026-08-14).</t>
         </is>
       </c>
       <c r="AF25" s="31" t="inlineStr">
@@ -8264,32 +8280,32 @@
       </c>
       <c r="AP25" s="24" t="inlineStr">
         <is>
-          <t>M80</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AQ25" s="24" t="inlineStr">
         <is>
-          <t>M80</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AR25" s="24" t="inlineStr">
         <is>
-          <t>M80</t>
+          <t>SK Nebula</t>
         </is>
       </c>
       <c r="AS25" s="24" t="inlineStr">
         <is>
-          <t>Team Envy</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AT25" s="24" t="inlineStr">
         <is>
-          <t>Team Envy</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AU25" s="24" t="inlineStr">
         <is>
-          <t>Team Envy</t>
+          <t>Twisted Minds Orchid</t>
         </is>
       </c>
       <c r="AV25" s="24" t="n"/>
@@ -8307,7 +8323,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+          <t>b7c1dabbbbc9554691b923884077a0c9e2fdb894454c83cbe181c9fcf1b2e71f</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8322,7 +8338,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>3e30c9a8fb6f01c0c89924e36259c4ce725d15ed0ed8c2c80c389169eabcc95f</t>
+          <t>b7c1dabbbbc9554691b923884077a0c9e2fdb894454c83cbe181c9fcf1b2e71f</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8342,7 +8358,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:36.244313Z</t>
+          <t>2026-08-13T17:16:25.757754Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8352,13 +8368,13 @@
       </c>
       <c r="BJ25" s="25" t="n"/>
       <c r="BK25" s="26" t="n">
-        <v>-144</v>
+        <v>113</v>
       </c>
       <c r="BL25" s="27" t="n">
-        <v>1.694444</v>
+        <v>2.13</v>
       </c>
       <c r="BM25" s="28" t="n">
-        <v>0.590164</v>
+        <v>0.469484</v>
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
@@ -8397,6 +8413,275 @@
         </is>
       </c>
     </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>b46dadb2889942e7</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:16:26.831639Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-14T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>79349</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>VALORANT</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>2GAME Esports</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.778643</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>0.309159</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-valorant-fur-2game-2026-08-14).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>2GAME Esports</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>2GAME Esports</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>2GAME Esports</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>FURIA Esports</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>b7c1dabbbbc9554691b923884077a0c9e2fdb894454c83cbe181c9fcf1b2e71f</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>b7c1dabbbbc9554691b923884077a0c9e2fdb894454c83cbe181c9fcf1b2e71f</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>valorant-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:16:26.300408Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
